--- a/pdtracker/cursive_Trial_Template.xlsx
+++ b/pdtracker/cursive_Trial_Template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,25 +49,6 @@
       <color rgb="000F172A"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="10"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -94,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -102,10 +83,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -513,8 +490,6 @@
           <t>B0G1TN136B</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -527,16 +502,6 @@
           <t>MOBHCQ5GJDRB3DUE</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>RSK01</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Rahul Shopperskart</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -549,12 +514,6 @@
           <t>35295295</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>RSK01</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -567,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="95" customWidth="1" min="1" max="1"/>
@@ -653,79 +612,17 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>NEW COLUMNS (optional — for Buy Box tracking):</t>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>4. Seller Code (Col C, optional) — your internal code (e.g. RSK01) to filter Reports by seller.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>4. Seller Code (Col C, OPTIONAL):</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Your internal code for this seller account (e.g. RSK01).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      If you manage products for multiple sellers, give each a unique code.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Used to filter the Reports per seller.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="8" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>5. Seller Name (Col D, OPTIONAL):</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      The EXACT seller name as shown by the marketplace.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Example: "Cursive World Pvt Ltd", "Rahul Shopperskart"</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Required to enable Buy Box Lost tracking for this product.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      Leave blank if you don't care about Buy Box tracking — that part is skipped.</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5. Seller Name (Col D, optional) — exact marketplace seller name. Required to enable Buy Box tracking for this product.</t>
         </is>
       </c>
     </row>

--- a/pdtracker/cursive_Trial_Template.xlsx
+++ b/pdtracker/cursive_Trial_Template.xlsx
@@ -178,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -218,9 +218,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -958,8 +955,8 @@
         <f>IF(C2="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E2" s="16" t="n"/>
-      <c r="F2" s="16" t="n"/>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="n"/>
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n"/>
@@ -1000,8 +997,8 @@
         <f>IF(C3="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
       <c r="G3" s="8" t="n"/>
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="8" t="n"/>
@@ -1042,8 +1039,8 @@
         <f>IF(C4="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
@@ -1084,8 +1081,8 @@
         <f>IF(C5="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E5" s="16" t="n"/>
-      <c r="F5" s="16" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="8" t="n"/>
@@ -1126,8 +1123,8 @@
         <f>IF(C6="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
       <c r="G6" s="8" t="n"/>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="8" t="n"/>
@@ -1168,8 +1165,8 @@
         <f>IF(C7="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="8" t="n"/>
@@ -1210,8 +1207,8 @@
         <f>IF(C8="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
@@ -1252,8 +1249,8 @@
         <f>IF(C9="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E9" s="16" t="n"/>
-      <c r="F9" s="16" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
       <c r="G9" s="8" t="n"/>
       <c r="H9" s="8" t="n"/>
       <c r="I9" s="8" t="n"/>
@@ -1294,8 +1291,8 @@
         <f>IF(C10="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
@@ -1336,8 +1333,8 @@
         <f>IF(C11="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="8" t="n"/>
       <c r="I11" s="8" t="n"/>
@@ -1376,8 +1373,8 @@
         <f>IF(C12="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
@@ -1416,8 +1413,8 @@
         <f>IF(C13="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="8" t="n"/>
       <c r="I13" s="8" t="n"/>
@@ -1456,8 +1453,8 @@
         <f>IF(C14="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
@@ -1496,8 +1493,8 @@
         <f>IF(C15="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
       <c r="I15" s="8" t="n"/>
@@ -1536,8 +1533,8 @@
         <f>IF(C16="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
       <c r="I16" s="8" t="n"/>
@@ -1576,8 +1573,8 @@
         <f>IF(C17="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
       <c r="I17" s="8" t="n"/>
@@ -1616,8 +1613,8 @@
         <f>IF(C18="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="8" t="n"/>
@@ -1656,8 +1653,8 @@
         <f>IF(C19="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
       <c r="I19" s="8" t="n"/>
@@ -1696,8 +1693,8 @@
         <f>IF(C20="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="n"/>
@@ -1736,8 +1733,8 @@
         <f>IF(C21="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
       <c r="I21" s="8" t="n"/>
@@ -1776,8 +1773,8 @@
         <f>IF(C22="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="8" t="n"/>
@@ -1816,8 +1813,8 @@
         <f>IF(C23="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
       <c r="I23" s="8" t="n"/>
@@ -1856,8 +1853,8 @@
         <f>IF(C24="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
@@ -1896,8 +1893,8 @@
         <f>IF(C25="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
       <c r="I25" s="8" t="n"/>
@@ -1936,8 +1933,8 @@
         <f>IF(C26="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="8" t="n"/>
@@ -1970,8 +1967,8 @@
         <f>IF(C27="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
       <c r="I27" s="8" t="n"/>
@@ -2004,8 +2001,8 @@
         <f>IF(C28="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="8" t="n"/>
@@ -2038,8 +2035,8 @@
         <f>IF(C29="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="8" t="n"/>
@@ -2072,8 +2069,8 @@
         <f>IF(C30="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="8" t="n"/>
       <c r="I30" s="8" t="n"/>
@@ -2106,8 +2103,8 @@
         <f>IF(C31="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="8" t="n"/>
@@ -2140,8 +2137,8 @@
         <f>IF(C32="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
       <c r="G32" s="8" t="n"/>
       <c r="H32" s="8" t="n"/>
       <c r="I32" s="8" t="n"/>
@@ -2174,8 +2171,8 @@
         <f>IF(C33="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
       <c r="G33" s="8" t="n"/>
       <c r="H33" s="8" t="n"/>
       <c r="I33" s="8" t="n"/>
@@ -2208,8 +2205,8 @@
         <f>IF(C34="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E34" s="16" t="n"/>
-      <c r="F34" s="16" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
       <c r="G34" s="8" t="n"/>
       <c r="H34" s="8" t="n"/>
       <c r="I34" s="8" t="n"/>
@@ -2242,8 +2239,8 @@
         <f>IF(C35="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E35" s="16" t="n"/>
-      <c r="F35" s="16" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
       <c r="G35" s="8" t="n"/>
       <c r="H35" s="8" t="n"/>
       <c r="I35" s="8" t="n"/>
@@ -2276,8 +2273,8 @@
         <f>IF(C36="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
       <c r="G36" s="8" t="n"/>
       <c r="H36" s="8" t="n"/>
       <c r="I36" s="8" t="n"/>
@@ -2310,8 +2307,8 @@
         <f>IF(C37="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="8" t="n"/>
@@ -2344,8 +2341,8 @@
         <f>IF(C38="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
       <c r="G38" s="8" t="n"/>
       <c r="H38" s="8" t="n"/>
       <c r="I38" s="8" t="n"/>
@@ -2378,8 +2375,8 @@
         <f>IF(C39="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="8" t="n"/>
@@ -2412,8 +2409,8 @@
         <f>IF(C40="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
       <c r="I40" s="8" t="n"/>
@@ -2446,8 +2443,8 @@
         <f>IF(C41="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
       <c r="I41" s="8" t="n"/>
@@ -2480,8 +2477,8 @@
         <f>IF(C42="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
       <c r="G42" s="8" t="n"/>
       <c r="H42" s="8" t="n"/>
       <c r="I42" s="8" t="n"/>
@@ -2514,8 +2511,8 @@
         <f>IF(C43="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
       <c r="G43" s="8" t="n"/>
       <c r="H43" s="8" t="n"/>
       <c r="I43" s="8" t="n"/>
@@ -2548,8 +2545,8 @@
         <f>IF(C44="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
       <c r="G44" s="8" t="n"/>
       <c r="H44" s="8" t="n"/>
       <c r="I44" s="8" t="n"/>
@@ -2582,8 +2579,8 @@
         <f>IF(C45="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
       <c r="G45" s="8" t="n"/>
       <c r="H45" s="8" t="n"/>
       <c r="I45" s="8" t="n"/>
@@ -2616,8 +2613,8 @@
         <f>IF(C46="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
       <c r="G46" s="8" t="n"/>
       <c r="H46" s="8" t="n"/>
       <c r="I46" s="8" t="n"/>
@@ -2650,8 +2647,8 @@
         <f>IF(C47="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
       <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="n"/>
       <c r="I47" s="8" t="n"/>
@@ -2684,8 +2681,8 @@
         <f>IF(C48="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
       <c r="I48" s="8" t="n"/>
@@ -2718,8 +2715,8 @@
         <f>IF(C49="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
       <c r="I49" s="8" t="n"/>
@@ -2752,8 +2749,8 @@
         <f>IF(C50="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
       <c r="I50" s="8" t="n"/>
@@ -2786,8 +2783,8 @@
         <f>IF(C51="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
       <c r="I51" s="8" t="n"/>
@@ -2820,8 +2817,8 @@
         <f>IF(C52="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
       <c r="I52" s="8" t="n"/>
@@ -2854,8 +2851,8 @@
         <f>IF(C53="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
       <c r="I53" s="8" t="n"/>
@@ -2888,8 +2885,8 @@
         <f>IF(C54="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
       <c r="I54" s="8" t="n"/>
@@ -2922,8 +2919,8 @@
         <f>IF(C55="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E55" s="16" t="n"/>
-      <c r="F55" s="16" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
       <c r="I55" s="8" t="n"/>
@@ -2956,8 +2953,8 @@
         <f>IF(C56="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="9" t="n"/>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
       <c r="I56" s="8" t="n"/>
@@ -2990,8 +2987,8 @@
         <f>IF(C57="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E57" s="16" t="n"/>
-      <c r="F57" s="16" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
       <c r="I57" s="8" t="n"/>
@@ -3024,8 +3021,8 @@
         <f>IF(C58="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E58" s="16" t="n"/>
-      <c r="F58" s="16" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="8" t="n"/>
       <c r="I58" s="8" t="n"/>
@@ -3058,8 +3055,8 @@
         <f>IF(C59="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E59" s="16" t="n"/>
-      <c r="F59" s="16" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
       <c r="I59" s="8" t="n"/>
@@ -3092,8 +3089,8 @@
         <f>IF(C60="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E60" s="16" t="n"/>
-      <c r="F60" s="16" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
       <c r="I60" s="8" t="n"/>
@@ -3126,8 +3123,8 @@
         <f>IF(C61="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E61" s="16" t="n"/>
-      <c r="F61" s="16" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
       <c r="I61" s="8" t="n"/>
@@ -3160,8 +3157,8 @@
         <f>IF(C62="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E62" s="16" t="n"/>
-      <c r="F62" s="16" t="n"/>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="9" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
       <c r="I62" s="8" t="n"/>
@@ -3194,8 +3191,8 @@
         <f>IF(C63="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E63" s="16" t="n"/>
-      <c r="F63" s="16" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
       <c r="I63" s="8" t="n"/>
@@ -3228,8 +3225,8 @@
         <f>IF(C64="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E64" s="16" t="n"/>
-      <c r="F64" s="16" t="n"/>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="9" t="n"/>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
       <c r="I64" s="8" t="n"/>
@@ -3262,8 +3259,8 @@
         <f>IF(C65="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E65" s="16" t="n"/>
-      <c r="F65" s="16" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
       <c r="I65" s="8" t="n"/>
@@ -3296,8 +3293,8 @@
         <f>IF(C66="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
       <c r="I66" s="8" t="n"/>
@@ -3330,8 +3327,8 @@
         <f>IF(C67="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E67" s="16" t="n"/>
-      <c r="F67" s="16" t="n"/>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="n"/>
       <c r="I67" s="8" t="n"/>
@@ -3364,8 +3361,8 @@
         <f>IF(C68="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E68" s="16" t="n"/>
-      <c r="F68" s="16" t="n"/>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="9" t="n"/>
       <c r="G68" s="8" t="n"/>
       <c r="H68" s="8" t="n"/>
       <c r="I68" s="8" t="n"/>
@@ -3398,8 +3395,8 @@
         <f>IF(C69="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E69" s="16" t="n"/>
-      <c r="F69" s="16" t="n"/>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="9" t="n"/>
       <c r="G69" s="8" t="n"/>
       <c r="H69" s="8" t="n"/>
       <c r="I69" s="8" t="n"/>
@@ -3432,8 +3429,8 @@
         <f>IF(C70="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E70" s="16" t="n"/>
-      <c r="F70" s="16" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="9" t="n"/>
       <c r="G70" s="8" t="n"/>
       <c r="H70" s="8" t="n"/>
       <c r="I70" s="8" t="n"/>
@@ -3466,8 +3463,8 @@
         <f>IF(C71="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E71" s="16" t="n"/>
-      <c r="F71" s="16" t="n"/>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="9" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
       <c r="I71" s="8" t="n"/>
@@ -3500,8 +3497,8 @@
         <f>IF(C72="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E72" s="16" t="n"/>
-      <c r="F72" s="16" t="n"/>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="9" t="n"/>
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="n"/>
       <c r="I72" s="8" t="n"/>
@@ -3534,8 +3531,8 @@
         <f>IF(C73="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E73" s="16" t="n"/>
-      <c r="F73" s="16" t="n"/>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="9" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
       <c r="I73" s="8" t="n"/>
@@ -3568,8 +3565,8 @@
         <f>IF(C74="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E74" s="16" t="n"/>
-      <c r="F74" s="16" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="9" t="n"/>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
       <c r="I74" s="8" t="n"/>
@@ -3602,8 +3599,8 @@
         <f>IF(C75="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E75" s="16" t="n"/>
-      <c r="F75" s="16" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
       <c r="I75" s="8" t="n"/>
@@ -3636,8 +3633,8 @@
         <f>IF(C76="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E76" s="16" t="n"/>
-      <c r="F76" s="16" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
       <c r="I76" s="8" t="n"/>
@@ -3670,8 +3667,8 @@
         <f>IF(C77="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E77" s="16" t="n"/>
-      <c r="F77" s="16" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
       <c r="I77" s="8" t="n"/>
@@ -3704,8 +3701,8 @@
         <f>IF(C78="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E78" s="16" t="n"/>
-      <c r="F78" s="16" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="9" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
       <c r="I78" s="8" t="n"/>
@@ -3738,8 +3735,8 @@
         <f>IF(C79="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E79" s="16" t="n"/>
-      <c r="F79" s="16" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="9" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
       <c r="I79" s="8" t="n"/>
@@ -3772,8 +3769,8 @@
         <f>IF(C80="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E80" s="16" t="n"/>
-      <c r="F80" s="16" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="n"/>
       <c r="G80" s="8" t="n"/>
       <c r="H80" s="8" t="n"/>
       <c r="I80" s="8" t="n"/>
@@ -3806,8 +3803,8 @@
         <f>IF(C81="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E81" s="16" t="n"/>
-      <c r="F81" s="16" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
       <c r="I81" s="8" t="n"/>
@@ -3840,8 +3837,8 @@
         <f>IF(C82="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E82" s="16" t="n"/>
-      <c r="F82" s="16" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="n"/>
       <c r="G82" s="8" t="n"/>
       <c r="H82" s="8" t="n"/>
       <c r="I82" s="8" t="n"/>
@@ -3874,8 +3871,8 @@
         <f>IF(C83="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E83" s="16" t="n"/>
-      <c r="F83" s="16" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="9" t="n"/>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
       <c r="I83" s="8" t="n"/>
@@ -3908,8 +3905,8 @@
         <f>IF(C84="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E84" s="16" t="n"/>
-      <c r="F84" s="16" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="n"/>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
       <c r="I84" s="8" t="n"/>
@@ -3942,8 +3939,8 @@
         <f>IF(C85="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E85" s="16" t="n"/>
-      <c r="F85" s="16" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
       <c r="I85" s="8" t="n"/>
@@ -3976,8 +3973,8 @@
         <f>IF(C86="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E86" s="16" t="n"/>
-      <c r="F86" s="16" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="9" t="n"/>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
       <c r="I86" s="8" t="n"/>
@@ -4010,8 +4007,8 @@
         <f>IF(C87="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E87" s="16" t="n"/>
-      <c r="F87" s="16" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="9" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
       <c r="I87" s="8" t="n"/>
@@ -4044,8 +4041,8 @@
         <f>IF(C88="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E88" s="16" t="n"/>
-      <c r="F88" s="16" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="9" t="n"/>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
       <c r="I88" s="8" t="n"/>
@@ -4078,8 +4075,8 @@
         <f>IF(C89="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E89" s="16" t="n"/>
-      <c r="F89" s="16" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
       <c r="I89" s="8" t="n"/>
@@ -4112,8 +4109,8 @@
         <f>IF(C90="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E90" s="16" t="n"/>
-      <c r="F90" s="16" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="9" t="n"/>
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="n"/>
       <c r="I90" s="8" t="n"/>
@@ -4146,8 +4143,8 @@
         <f>IF(C91="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E91" s="16" t="n"/>
-      <c r="F91" s="16" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="n"/>
       <c r="I91" s="8" t="n"/>
@@ -4180,8 +4177,8 @@
         <f>IF(C92="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E92" s="16" t="n"/>
-      <c r="F92" s="16" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="9" t="n"/>
       <c r="G92" s="8" t="n"/>
       <c r="H92" s="8" t="n"/>
       <c r="I92" s="8" t="n"/>
@@ -4214,8 +4211,8 @@
         <f>IF(C93="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E93" s="16" t="n"/>
-      <c r="F93" s="16" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="n"/>
       <c r="I93" s="8" t="n"/>
@@ -4248,8 +4245,8 @@
         <f>IF(C94="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E94" s="16" t="n"/>
-      <c r="F94" s="16" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
       <c r="G94" s="8" t="n"/>
       <c r="H94" s="8" t="n"/>
       <c r="I94" s="8" t="n"/>
@@ -4282,8 +4279,8 @@
         <f>IF(C95="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E95" s="16" t="n"/>
-      <c r="F95" s="16" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="9" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
       <c r="I95" s="8" t="n"/>
@@ -4316,8 +4313,8 @@
         <f>IF(C96="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E96" s="16" t="n"/>
-      <c r="F96" s="16" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
       <c r="I96" s="8" t="n"/>
@@ -4350,8 +4347,8 @@
         <f>IF(C97="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E97" s="16" t="n"/>
-      <c r="F97" s="16" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="9" t="n"/>
       <c r="G97" s="8" t="n"/>
       <c r="H97" s="8" t="n"/>
       <c r="I97" s="8" t="n"/>
@@ -4384,8 +4381,8 @@
         <f>IF(C98="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E98" s="16" t="n"/>
-      <c r="F98" s="16" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="n"/>
       <c r="I98" s="8" t="n"/>
@@ -4418,8 +4415,8 @@
         <f>IF(C99="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E99" s="16" t="n"/>
-      <c r="F99" s="16" t="n"/>
+      <c r="E99" s="9" t="n"/>
+      <c r="F99" s="9" t="n"/>
       <c r="G99" s="8" t="n"/>
       <c r="H99" s="8" t="n"/>
       <c r="I99" s="8" t="n"/>
@@ -4452,8 +4449,8 @@
         <f>IF(C100="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E100" s="16" t="n"/>
-      <c r="F100" s="16" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="9" t="n"/>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="n"/>
       <c r="I100" s="8" t="n"/>
@@ -4486,8 +4483,8 @@
         <f>IF(C101="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E101" s="16" t="n"/>
-      <c r="F101" s="16" t="n"/>
+      <c r="E101" s="9" t="n"/>
+      <c r="F101" s="9" t="n"/>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="n"/>
       <c r="I101" s="8" t="n"/>
@@ -4520,8 +4517,8 @@
         <f>IF(C102="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E102" s="16" t="n"/>
-      <c r="F102" s="16" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="9" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
       <c r="I102" s="8" t="n"/>
@@ -4554,8 +4551,8 @@
         <f>IF(C103="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E103" s="16" t="n"/>
-      <c r="F103" s="16" t="n"/>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="9" t="n"/>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
       <c r="I103" s="8" t="n"/>
@@ -4588,8 +4585,8 @@
         <f>IF(C104="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E104" s="16" t="n"/>
-      <c r="F104" s="16" t="n"/>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="9" t="n"/>
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="n"/>
       <c r="I104" s="8" t="n"/>
@@ -4622,8 +4619,8 @@
         <f>IF(C105="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E105" s="16" t="n"/>
-      <c r="F105" s="16" t="n"/>
+      <c r="E105" s="9" t="n"/>
+      <c r="F105" s="9" t="n"/>
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="8" t="n"/>
       <c r="I105" s="8" t="n"/>
@@ -4656,8 +4653,8 @@
         <f>IF(C106="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E106" s="16" t="n"/>
-      <c r="F106" s="16" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="9" t="n"/>
       <c r="G106" s="8" t="n"/>
       <c r="H106" s="8" t="n"/>
       <c r="I106" s="8" t="n"/>
@@ -4690,8 +4687,8 @@
         <f>IF(C107="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E107" s="16" t="n"/>
-      <c r="F107" s="16" t="n"/>
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="9" t="n"/>
       <c r="G107" s="8" t="n"/>
       <c r="H107" s="8" t="n"/>
       <c r="I107" s="8" t="n"/>
@@ -4724,8 +4721,8 @@
         <f>IF(C108="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E108" s="16" t="n"/>
-      <c r="F108" s="16" t="n"/>
+      <c r="E108" s="9" t="n"/>
+      <c r="F108" s="9" t="n"/>
       <c r="G108" s="8" t="n"/>
       <c r="H108" s="8" t="n"/>
       <c r="I108" s="8" t="n"/>
@@ -4758,8 +4755,8 @@
         <f>IF(C109="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E109" s="16" t="n"/>
-      <c r="F109" s="16" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="9" t="n"/>
       <c r="G109" s="8" t="n"/>
       <c r="H109" s="8" t="n"/>
       <c r="I109" s="8" t="n"/>
@@ -4792,8 +4789,8 @@
         <f>IF(C110="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E110" s="16" t="n"/>
-      <c r="F110" s="16" t="n"/>
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="9" t="n"/>
       <c r="G110" s="8" t="n"/>
       <c r="H110" s="8" t="n"/>
       <c r="I110" s="8" t="n"/>
@@ -4826,8 +4823,8 @@
         <f>IF(C111="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E111" s="16" t="n"/>
-      <c r="F111" s="16" t="n"/>
+      <c r="E111" s="9" t="n"/>
+      <c r="F111" s="9" t="n"/>
       <c r="G111" s="8" t="n"/>
       <c r="H111" s="8" t="n"/>
       <c r="I111" s="8" t="n"/>
@@ -4860,8 +4857,8 @@
         <f>IF(C112="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E112" s="16" t="n"/>
-      <c r="F112" s="16" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="9" t="n"/>
       <c r="G112" s="8" t="n"/>
       <c r="H112" s="8" t="n"/>
       <c r="I112" s="8" t="n"/>
@@ -4894,8 +4891,8 @@
         <f>IF(C113="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E113" s="16" t="n"/>
-      <c r="F113" s="16" t="n"/>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="9" t="n"/>
       <c r="G113" s="8" t="n"/>
       <c r="H113" s="8" t="n"/>
       <c r="I113" s="8" t="n"/>
@@ -4928,8 +4925,8 @@
         <f>IF(C114="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E114" s="16" t="n"/>
-      <c r="F114" s="16" t="n"/>
+      <c r="E114" s="9" t="n"/>
+      <c r="F114" s="9" t="n"/>
       <c r="G114" s="8" t="n"/>
       <c r="H114" s="8" t="n"/>
       <c r="I114" s="8" t="n"/>
@@ -4962,8 +4959,8 @@
         <f>IF(C115="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E115" s="16" t="n"/>
-      <c r="F115" s="16" t="n"/>
+      <c r="E115" s="9" t="n"/>
+      <c r="F115" s="9" t="n"/>
       <c r="G115" s="8" t="n"/>
       <c r="H115" s="8" t="n"/>
       <c r="I115" s="8" t="n"/>
@@ -4996,8 +4993,8 @@
         <f>IF(C116="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E116" s="16" t="n"/>
-      <c r="F116" s="16" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="9" t="n"/>
       <c r="G116" s="8" t="n"/>
       <c r="H116" s="8" t="n"/>
       <c r="I116" s="8" t="n"/>
@@ -5030,8 +5027,8 @@
         <f>IF(C117="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E117" s="16" t="n"/>
-      <c r="F117" s="16" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="9" t="n"/>
       <c r="G117" s="8" t="n"/>
       <c r="H117" s="8" t="n"/>
       <c r="I117" s="8" t="n"/>
@@ -5064,8 +5061,8 @@
         <f>IF(C118="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E118" s="16" t="n"/>
-      <c r="F118" s="16" t="n"/>
+      <c r="E118" s="9" t="n"/>
+      <c r="F118" s="9" t="n"/>
       <c r="G118" s="8" t="n"/>
       <c r="H118" s="8" t="n"/>
       <c r="I118" s="8" t="n"/>
@@ -5098,8 +5095,8 @@
         <f>IF(C119="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E119" s="16" t="n"/>
-      <c r="F119" s="16" t="n"/>
+      <c r="E119" s="9" t="n"/>
+      <c r="F119" s="9" t="n"/>
       <c r="G119" s="8" t="n"/>
       <c r="H119" s="8" t="n"/>
       <c r="I119" s="8" t="n"/>
@@ -5132,8 +5129,8 @@
         <f>IF(C120="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E120" s="16" t="n"/>
-      <c r="F120" s="16" t="n"/>
+      <c r="E120" s="9" t="n"/>
+      <c r="F120" s="9" t="n"/>
       <c r="G120" s="8" t="n"/>
       <c r="H120" s="8" t="n"/>
       <c r="I120" s="8" t="n"/>
@@ -5166,8 +5163,8 @@
         <f>IF(C121="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E121" s="16" t="n"/>
-      <c r="F121" s="16" t="n"/>
+      <c r="E121" s="9" t="n"/>
+      <c r="F121" s="9" t="n"/>
       <c r="G121" s="8" t="n"/>
       <c r="H121" s="8" t="n"/>
       <c r="I121" s="8" t="n"/>
@@ -5200,8 +5197,8 @@
         <f>IF(C122="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E122" s="16" t="n"/>
-      <c r="F122" s="16" t="n"/>
+      <c r="E122" s="9" t="n"/>
+      <c r="F122" s="9" t="n"/>
       <c r="G122" s="8" t="n"/>
       <c r="H122" s="8" t="n"/>
       <c r="I122" s="8" t="n"/>
@@ -5234,8 +5231,8 @@
         <f>IF(C123="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E123" s="16" t="n"/>
-      <c r="F123" s="16" t="n"/>
+      <c r="E123" s="9" t="n"/>
+      <c r="F123" s="9" t="n"/>
       <c r="G123" s="8" t="n"/>
       <c r="H123" s="8" t="n"/>
       <c r="I123" s="8" t="n"/>
@@ -5268,8 +5265,8 @@
         <f>IF(C124="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E124" s="16" t="n"/>
-      <c r="F124" s="16" t="n"/>
+      <c r="E124" s="9" t="n"/>
+      <c r="F124" s="9" t="n"/>
       <c r="G124" s="8" t="n"/>
       <c r="H124" s="8" t="n"/>
       <c r="I124" s="8" t="n"/>
@@ -5302,8 +5299,8 @@
         <f>IF(C125="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E125" s="16" t="n"/>
-      <c r="F125" s="16" t="n"/>
+      <c r="E125" s="9" t="n"/>
+      <c r="F125" s="9" t="n"/>
       <c r="G125" s="8" t="n"/>
       <c r="H125" s="8" t="n"/>
       <c r="I125" s="8" t="n"/>
@@ -5336,8 +5333,8 @@
         <f>IF(C126="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E126" s="16" t="n"/>
-      <c r="F126" s="16" t="n"/>
+      <c r="E126" s="9" t="n"/>
+      <c r="F126" s="9" t="n"/>
       <c r="G126" s="8" t="n"/>
       <c r="H126" s="8" t="n"/>
       <c r="I126" s="8" t="n"/>
@@ -5370,8 +5367,8 @@
         <f>IF(C127="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E127" s="16" t="n"/>
-      <c r="F127" s="16" t="n"/>
+      <c r="E127" s="9" t="n"/>
+      <c r="F127" s="9" t="n"/>
       <c r="G127" s="8" t="n"/>
       <c r="H127" s="8" t="n"/>
       <c r="I127" s="8" t="n"/>
@@ -5404,8 +5401,8 @@
         <f>IF(C128="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E128" s="16" t="n"/>
-      <c r="F128" s="16" t="n"/>
+      <c r="E128" s="9" t="n"/>
+      <c r="F128" s="9" t="n"/>
       <c r="G128" s="8" t="n"/>
       <c r="H128" s="8" t="n"/>
       <c r="I128" s="8" t="n"/>
@@ -5438,8 +5435,8 @@
         <f>IF(C129="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E129" s="16" t="n"/>
-      <c r="F129" s="16" t="n"/>
+      <c r="E129" s="9" t="n"/>
+      <c r="F129" s="9" t="n"/>
       <c r="G129" s="8" t="n"/>
       <c r="H129" s="8" t="n"/>
       <c r="I129" s="8" t="n"/>
@@ -5472,8 +5469,8 @@
         <f>IF(C130="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E130" s="16" t="n"/>
-      <c r="F130" s="16" t="n"/>
+      <c r="E130" s="9" t="n"/>
+      <c r="F130" s="9" t="n"/>
       <c r="G130" s="8" t="n"/>
       <c r="H130" s="8" t="n"/>
       <c r="I130" s="8" t="n"/>
@@ -5506,8 +5503,8 @@
         <f>IF(C131="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E131" s="16" t="n"/>
-      <c r="F131" s="16" t="n"/>
+      <c r="E131" s="9" t="n"/>
+      <c r="F131" s="9" t="n"/>
       <c r="G131" s="8" t="n"/>
       <c r="H131" s="8" t="n"/>
       <c r="I131" s="8" t="n"/>
@@ -5540,8 +5537,8 @@
         <f>IF(C132="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E132" s="16" t="n"/>
-      <c r="F132" s="16" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="9" t="n"/>
       <c r="G132" s="8" t="n"/>
       <c r="H132" s="8" t="n"/>
       <c r="I132" s="8" t="n"/>
@@ -5574,8 +5571,8 @@
         <f>IF(C133="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E133" s="16" t="n"/>
-      <c r="F133" s="16" t="n"/>
+      <c r="E133" s="9" t="n"/>
+      <c r="F133" s="9" t="n"/>
       <c r="G133" s="8" t="n"/>
       <c r="H133" s="8" t="n"/>
       <c r="I133" s="8" t="n"/>
@@ -5608,8 +5605,8 @@
         <f>IF(C134="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E134" s="16" t="n"/>
-      <c r="F134" s="16" t="n"/>
+      <c r="E134" s="9" t="n"/>
+      <c r="F134" s="9" t="n"/>
       <c r="G134" s="8" t="n"/>
       <c r="H134" s="8" t="n"/>
       <c r="I134" s="8" t="n"/>
@@ -5642,8 +5639,8 @@
         <f>IF(C135="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E135" s="16" t="n"/>
-      <c r="F135" s="16" t="n"/>
+      <c r="E135" s="9" t="n"/>
+      <c r="F135" s="9" t="n"/>
       <c r="G135" s="8" t="n"/>
       <c r="H135" s="8" t="n"/>
       <c r="I135" s="8" t="n"/>
@@ -5676,8 +5673,8 @@
         <f>IF(C136="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E136" s="16" t="n"/>
-      <c r="F136" s="16" t="n"/>
+      <c r="E136" s="9" t="n"/>
+      <c r="F136" s="9" t="n"/>
       <c r="G136" s="8" t="n"/>
       <c r="H136" s="8" t="n"/>
       <c r="I136" s="8" t="n"/>
@@ -5710,8 +5707,8 @@
         <f>IF(C137="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E137" s="16" t="n"/>
-      <c r="F137" s="16" t="n"/>
+      <c r="E137" s="9" t="n"/>
+      <c r="F137" s="9" t="n"/>
       <c r="G137" s="8" t="n"/>
       <c r="H137" s="8" t="n"/>
       <c r="I137" s="8" t="n"/>
@@ -5744,8 +5741,8 @@
         <f>IF(C138="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E138" s="16" t="n"/>
-      <c r="F138" s="16" t="n"/>
+      <c r="E138" s="9" t="n"/>
+      <c r="F138" s="9" t="n"/>
       <c r="G138" s="8" t="n"/>
       <c r="H138" s="8" t="n"/>
       <c r="I138" s="8" t="n"/>
@@ -5778,8 +5775,8 @@
         <f>IF(C139="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E139" s="16" t="n"/>
-      <c r="F139" s="16" t="n"/>
+      <c r="E139" s="9" t="n"/>
+      <c r="F139" s="9" t="n"/>
       <c r="G139" s="8" t="n"/>
       <c r="H139" s="8" t="n"/>
       <c r="I139" s="8" t="n"/>
@@ -5812,8 +5809,8 @@
         <f>IF(C140="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E140" s="16" t="n"/>
-      <c r="F140" s="16" t="n"/>
+      <c r="E140" s="9" t="n"/>
+      <c r="F140" s="9" t="n"/>
       <c r="G140" s="8" t="n"/>
       <c r="H140" s="8" t="n"/>
       <c r="I140" s="8" t="n"/>
@@ -5846,8 +5843,8 @@
         <f>IF(C141="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E141" s="16" t="n"/>
-      <c r="F141" s="16" t="n"/>
+      <c r="E141" s="9" t="n"/>
+      <c r="F141" s="9" t="n"/>
       <c r="G141" s="8" t="n"/>
       <c r="H141" s="8" t="n"/>
       <c r="I141" s="8" t="n"/>
@@ -5880,8 +5877,8 @@
         <f>IF(C142="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E142" s="16" t="n"/>
-      <c r="F142" s="16" t="n"/>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="9" t="n"/>
       <c r="G142" s="8" t="n"/>
       <c r="H142" s="8" t="n"/>
       <c r="I142" s="8" t="n"/>
@@ -5914,8 +5911,8 @@
         <f>IF(C143="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E143" s="16" t="n"/>
-      <c r="F143" s="16" t="n"/>
+      <c r="E143" s="9" t="n"/>
+      <c r="F143" s="9" t="n"/>
       <c r="G143" s="8" t="n"/>
       <c r="H143" s="8" t="n"/>
       <c r="I143" s="8" t="n"/>
@@ -5948,8 +5945,8 @@
         <f>IF(C144="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E144" s="16" t="n"/>
-      <c r="F144" s="16" t="n"/>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="n"/>
       <c r="G144" s="8" t="n"/>
       <c r="H144" s="8" t="n"/>
       <c r="I144" s="8" t="n"/>
@@ -5982,8 +5979,8 @@
         <f>IF(C145="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E145" s="16" t="n"/>
-      <c r="F145" s="16" t="n"/>
+      <c r="E145" s="9" t="n"/>
+      <c r="F145" s="9" t="n"/>
       <c r="G145" s="8" t="n"/>
       <c r="H145" s="8" t="n"/>
       <c r="I145" s="8" t="n"/>
@@ -6016,8 +6013,8 @@
         <f>IF(C146="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E146" s="16" t="n"/>
-      <c r="F146" s="16" t="n"/>
+      <c r="E146" s="9" t="n"/>
+      <c r="F146" s="9" t="n"/>
       <c r="G146" s="8" t="n"/>
       <c r="H146" s="8" t="n"/>
       <c r="I146" s="8" t="n"/>
@@ -6050,8 +6047,8 @@
         <f>IF(C147="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E147" s="16" t="n"/>
-      <c r="F147" s="16" t="n"/>
+      <c r="E147" s="9" t="n"/>
+      <c r="F147" s="9" t="n"/>
       <c r="G147" s="8" t="n"/>
       <c r="H147" s="8" t="n"/>
       <c r="I147" s="8" t="n"/>
@@ -6084,8 +6081,8 @@
         <f>IF(C148="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E148" s="16" t="n"/>
-      <c r="F148" s="16" t="n"/>
+      <c r="E148" s="9" t="n"/>
+      <c r="F148" s="9" t="n"/>
       <c r="G148" s="8" t="n"/>
       <c r="H148" s="8" t="n"/>
       <c r="I148" s="8" t="n"/>
@@ -6118,8 +6115,8 @@
         <f>IF(C149="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E149" s="16" t="n"/>
-      <c r="F149" s="16" t="n"/>
+      <c r="E149" s="9" t="n"/>
+      <c r="F149" s="9" t="n"/>
       <c r="G149" s="8" t="n"/>
       <c r="H149" s="8" t="n"/>
       <c r="I149" s="8" t="n"/>
@@ -6152,8 +6149,8 @@
         <f>IF(C150="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E150" s="16" t="n"/>
-      <c r="F150" s="16" t="n"/>
+      <c r="E150" s="9" t="n"/>
+      <c r="F150" s="9" t="n"/>
       <c r="G150" s="8" t="n"/>
       <c r="H150" s="8" t="n"/>
       <c r="I150" s="8" t="n"/>
@@ -6186,8 +6183,8 @@
         <f>IF(C151="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E151" s="16" t="n"/>
-      <c r="F151" s="16" t="n"/>
+      <c r="E151" s="9" t="n"/>
+      <c r="F151" s="9" t="n"/>
       <c r="G151" s="8" t="n"/>
       <c r="H151" s="8" t="n"/>
       <c r="I151" s="8" t="n"/>
@@ -6220,8 +6217,8 @@
         <f>IF(C152="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E152" s="16" t="n"/>
-      <c r="F152" s="16" t="n"/>
+      <c r="E152" s="9" t="n"/>
+      <c r="F152" s="9" t="n"/>
       <c r="G152" s="8" t="n"/>
       <c r="H152" s="8" t="n"/>
       <c r="I152" s="8" t="n"/>
@@ -6254,8 +6251,8 @@
         <f>IF(C153="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E153" s="16" t="n"/>
-      <c r="F153" s="16" t="n"/>
+      <c r="E153" s="9" t="n"/>
+      <c r="F153" s="9" t="n"/>
       <c r="G153" s="8" t="n"/>
       <c r="H153" s="8" t="n"/>
       <c r="I153" s="8" t="n"/>
@@ -6288,8 +6285,8 @@
         <f>IF(C154="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E154" s="16" t="n"/>
-      <c r="F154" s="16" t="n"/>
+      <c r="E154" s="9" t="n"/>
+      <c r="F154" s="9" t="n"/>
       <c r="G154" s="8" t="n"/>
       <c r="H154" s="8" t="n"/>
       <c r="I154" s="8" t="n"/>
@@ -6322,8 +6319,8 @@
         <f>IF(C155="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E155" s="16" t="n"/>
-      <c r="F155" s="16" t="n"/>
+      <c r="E155" s="9" t="n"/>
+      <c r="F155" s="9" t="n"/>
       <c r="G155" s="8" t="n"/>
       <c r="H155" s="8" t="n"/>
       <c r="I155" s="8" t="n"/>
@@ -6356,8 +6353,8 @@
         <f>IF(C156="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E156" s="16" t="n"/>
-      <c r="F156" s="16" t="n"/>
+      <c r="E156" s="9" t="n"/>
+      <c r="F156" s="9" t="n"/>
       <c r="G156" s="8" t="n"/>
       <c r="H156" s="8" t="n"/>
       <c r="I156" s="8" t="n"/>
@@ -6390,8 +6387,8 @@
         <f>IF(C157="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E157" s="16" t="n"/>
-      <c r="F157" s="16" t="n"/>
+      <c r="E157" s="9" t="n"/>
+      <c r="F157" s="9" t="n"/>
       <c r="G157" s="8" t="n"/>
       <c r="H157" s="8" t="n"/>
       <c r="I157" s="8" t="n"/>
@@ -6424,8 +6421,8 @@
         <f>IF(C158="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E158" s="16" t="n"/>
-      <c r="F158" s="16" t="n"/>
+      <c r="E158" s="9" t="n"/>
+      <c r="F158" s="9" t="n"/>
       <c r="G158" s="8" t="n"/>
       <c r="H158" s="8" t="n"/>
       <c r="I158" s="8" t="n"/>
@@ -6458,8 +6455,8 @@
         <f>IF(C159="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E159" s="16" t="n"/>
-      <c r="F159" s="16" t="n"/>
+      <c r="E159" s="9" t="n"/>
+      <c r="F159" s="9" t="n"/>
       <c r="G159" s="8" t="n"/>
       <c r="H159" s="8" t="n"/>
       <c r="I159" s="8" t="n"/>
@@ -6492,8 +6489,8 @@
         <f>IF(C160="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E160" s="16" t="n"/>
-      <c r="F160" s="16" t="n"/>
+      <c r="E160" s="9" t="n"/>
+      <c r="F160" s="9" t="n"/>
       <c r="G160" s="8" t="n"/>
       <c r="H160" s="8" t="n"/>
       <c r="I160" s="8" t="n"/>
@@ -6526,8 +6523,8 @@
         <f>IF(C161="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E161" s="16" t="n"/>
-      <c r="F161" s="16" t="n"/>
+      <c r="E161" s="9" t="n"/>
+      <c r="F161" s="9" t="n"/>
       <c r="G161" s="8" t="n"/>
       <c r="H161" s="8" t="n"/>
       <c r="I161" s="8" t="n"/>
@@ -6560,8 +6557,8 @@
         <f>IF(C162="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E162" s="16" t="n"/>
-      <c r="F162" s="16" t="n"/>
+      <c r="E162" s="9" t="n"/>
+      <c r="F162" s="9" t="n"/>
       <c r="G162" s="8" t="n"/>
       <c r="H162" s="8" t="n"/>
       <c r="I162" s="8" t="n"/>
@@ -6594,8 +6591,8 @@
         <f>IF(C163="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E163" s="16" t="n"/>
-      <c r="F163" s="16" t="n"/>
+      <c r="E163" s="9" t="n"/>
+      <c r="F163" s="9" t="n"/>
       <c r="G163" s="8" t="n"/>
       <c r="H163" s="8" t="n"/>
       <c r="I163" s="8" t="n"/>
@@ -6628,8 +6625,8 @@
         <f>IF(C164="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E164" s="16" t="n"/>
-      <c r="F164" s="16" t="n"/>
+      <c r="E164" s="9" t="n"/>
+      <c r="F164" s="9" t="n"/>
       <c r="G164" s="8" t="n"/>
       <c r="H164" s="8" t="n"/>
       <c r="I164" s="8" t="n"/>
@@ -6662,8 +6659,8 @@
         <f>IF(C165="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E165" s="16" t="n"/>
-      <c r="F165" s="16" t="n"/>
+      <c r="E165" s="9" t="n"/>
+      <c r="F165" s="9" t="n"/>
       <c r="G165" s="8" t="n"/>
       <c r="H165" s="8" t="n"/>
       <c r="I165" s="8" t="n"/>
@@ -6696,8 +6693,8 @@
         <f>IF(C166="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E166" s="16" t="n"/>
-      <c r="F166" s="16" t="n"/>
+      <c r="E166" s="9" t="n"/>
+      <c r="F166" s="9" t="n"/>
       <c r="G166" s="8" t="n"/>
       <c r="H166" s="8" t="n"/>
       <c r="I166" s="8" t="n"/>
@@ -6730,8 +6727,8 @@
         <f>IF(C167="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E167" s="16" t="n"/>
-      <c r="F167" s="16" t="n"/>
+      <c r="E167" s="9" t="n"/>
+      <c r="F167" s="9" t="n"/>
       <c r="G167" s="8" t="n"/>
       <c r="H167" s="8" t="n"/>
       <c r="I167" s="8" t="n"/>
@@ -6764,8 +6761,8 @@
         <f>IF(C168="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E168" s="16" t="n"/>
-      <c r="F168" s="16" t="n"/>
+      <c r="E168" s="9" t="n"/>
+      <c r="F168" s="9" t="n"/>
       <c r="G168" s="8" t="n"/>
       <c r="H168" s="8" t="n"/>
       <c r="I168" s="8" t="n"/>
@@ -6798,8 +6795,8 @@
         <f>IF(C169="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E169" s="16" t="n"/>
-      <c r="F169" s="16" t="n"/>
+      <c r="E169" s="9" t="n"/>
+      <c r="F169" s="9" t="n"/>
       <c r="G169" s="8" t="n"/>
       <c r="H169" s="8" t="n"/>
       <c r="I169" s="8" t="n"/>
@@ -6832,8 +6829,8 @@
         <f>IF(C170="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E170" s="16" t="n"/>
-      <c r="F170" s="16" t="n"/>
+      <c r="E170" s="9" t="n"/>
+      <c r="F170" s="9" t="n"/>
       <c r="G170" s="8" t="n"/>
       <c r="H170" s="8" t="n"/>
       <c r="I170" s="8" t="n"/>
@@ -6866,8 +6863,8 @@
         <f>IF(C171="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E171" s="16" t="n"/>
-      <c r="F171" s="16" t="n"/>
+      <c r="E171" s="9" t="n"/>
+      <c r="F171" s="9" t="n"/>
       <c r="G171" s="8" t="n"/>
       <c r="H171" s="8" t="n"/>
       <c r="I171" s="8" t="n"/>
@@ -6900,8 +6897,8 @@
         <f>IF(C172="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E172" s="16" t="n"/>
-      <c r="F172" s="16" t="n"/>
+      <c r="E172" s="9" t="n"/>
+      <c r="F172" s="9" t="n"/>
       <c r="G172" s="8" t="n"/>
       <c r="H172" s="8" t="n"/>
       <c r="I172" s="8" t="n"/>
@@ -6934,8 +6931,8 @@
         <f>IF(C173="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E173" s="16" t="n"/>
-      <c r="F173" s="16" t="n"/>
+      <c r="E173" s="9" t="n"/>
+      <c r="F173" s="9" t="n"/>
       <c r="G173" s="8" t="n"/>
       <c r="H173" s="8" t="n"/>
       <c r="I173" s="8" t="n"/>
@@ -6968,8 +6965,8 @@
         <f>IF(C174="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E174" s="16" t="n"/>
-      <c r="F174" s="16" t="n"/>
+      <c r="E174" s="9" t="n"/>
+      <c r="F174" s="9" t="n"/>
       <c r="G174" s="8" t="n"/>
       <c r="H174" s="8" t="n"/>
       <c r="I174" s="8" t="n"/>
@@ -7002,8 +6999,8 @@
         <f>IF(C175="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E175" s="16" t="n"/>
-      <c r="F175" s="16" t="n"/>
+      <c r="E175" s="9" t="n"/>
+      <c r="F175" s="9" t="n"/>
       <c r="G175" s="8" t="n"/>
       <c r="H175" s="8" t="n"/>
       <c r="I175" s="8" t="n"/>
@@ -7036,8 +7033,8 @@
         <f>IF(C176="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E176" s="16" t="n"/>
-      <c r="F176" s="16" t="n"/>
+      <c r="E176" s="9" t="n"/>
+      <c r="F176" s="9" t="n"/>
       <c r="G176" s="8" t="n"/>
       <c r="H176" s="8" t="n"/>
       <c r="I176" s="8" t="n"/>
@@ -7070,8 +7067,8 @@
         <f>IF(C177="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E177" s="16" t="n"/>
-      <c r="F177" s="16" t="n"/>
+      <c r="E177" s="9" t="n"/>
+      <c r="F177" s="9" t="n"/>
       <c r="G177" s="8" t="n"/>
       <c r="H177" s="8" t="n"/>
       <c r="I177" s="8" t="n"/>
@@ -7104,8 +7101,8 @@
         <f>IF(C178="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E178" s="16" t="n"/>
-      <c r="F178" s="16" t="n"/>
+      <c r="E178" s="9" t="n"/>
+      <c r="F178" s="9" t="n"/>
       <c r="G178" s="8" t="n"/>
       <c r="H178" s="8" t="n"/>
       <c r="I178" s="8" t="n"/>
@@ -7138,8 +7135,8 @@
         <f>IF(C179="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E179" s="16" t="n"/>
-      <c r="F179" s="16" t="n"/>
+      <c r="E179" s="9" t="n"/>
+      <c r="F179" s="9" t="n"/>
       <c r="G179" s="8" t="n"/>
       <c r="H179" s="8" t="n"/>
       <c r="I179" s="8" t="n"/>
@@ -7172,8 +7169,8 @@
         <f>IF(C180="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E180" s="16" t="n"/>
-      <c r="F180" s="16" t="n"/>
+      <c r="E180" s="9" t="n"/>
+      <c r="F180" s="9" t="n"/>
       <c r="G180" s="8" t="n"/>
       <c r="H180" s="8" t="n"/>
       <c r="I180" s="8" t="n"/>
@@ -7206,8 +7203,8 @@
         <f>IF(C181="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E181" s="16" t="n"/>
-      <c r="F181" s="16" t="n"/>
+      <c r="E181" s="9" t="n"/>
+      <c r="F181" s="9" t="n"/>
       <c r="G181" s="8" t="n"/>
       <c r="H181" s="8" t="n"/>
       <c r="I181" s="8" t="n"/>
@@ -7240,8 +7237,8 @@
         <f>IF(C182="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E182" s="16" t="n"/>
-      <c r="F182" s="16" t="n"/>
+      <c r="E182" s="9" t="n"/>
+      <c r="F182" s="9" t="n"/>
       <c r="G182" s="8" t="n"/>
       <c r="H182" s="8" t="n"/>
       <c r="I182" s="8" t="n"/>
@@ -7274,8 +7271,8 @@
         <f>IF(C183="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E183" s="16" t="n"/>
-      <c r="F183" s="16" t="n"/>
+      <c r="E183" s="9" t="n"/>
+      <c r="F183" s="9" t="n"/>
       <c r="G183" s="8" t="n"/>
       <c r="H183" s="8" t="n"/>
       <c r="I183" s="8" t="n"/>
@@ -7308,8 +7305,8 @@
         <f>IF(C184="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E184" s="16" t="n"/>
-      <c r="F184" s="16" t="n"/>
+      <c r="E184" s="9" t="n"/>
+      <c r="F184" s="9" t="n"/>
       <c r="G184" s="8" t="n"/>
       <c r="H184" s="8" t="n"/>
       <c r="I184" s="8" t="n"/>
@@ -7342,8 +7339,8 @@
         <f>IF(C185="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E185" s="16" t="n"/>
-      <c r="F185" s="16" t="n"/>
+      <c r="E185" s="9" t="n"/>
+      <c r="F185" s="9" t="n"/>
       <c r="G185" s="8" t="n"/>
       <c r="H185" s="8" t="n"/>
       <c r="I185" s="8" t="n"/>
@@ -7376,8 +7373,8 @@
         <f>IF(C186="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E186" s="16" t="n"/>
-      <c r="F186" s="16" t="n"/>
+      <c r="E186" s="9" t="n"/>
+      <c r="F186" s="9" t="n"/>
       <c r="G186" s="8" t="n"/>
       <c r="H186" s="8" t="n"/>
       <c r="I186" s="8" t="n"/>
@@ -7410,8 +7407,8 @@
         <f>IF(C187="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E187" s="16" t="n"/>
-      <c r="F187" s="16" t="n"/>
+      <c r="E187" s="9" t="n"/>
+      <c r="F187" s="9" t="n"/>
       <c r="G187" s="8" t="n"/>
       <c r="H187" s="8" t="n"/>
       <c r="I187" s="8" t="n"/>
@@ -7444,8 +7441,8 @@
         <f>IF(C188="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E188" s="16" t="n"/>
-      <c r="F188" s="16" t="n"/>
+      <c r="E188" s="9" t="n"/>
+      <c r="F188" s="9" t="n"/>
       <c r="G188" s="8" t="n"/>
       <c r="H188" s="8" t="n"/>
       <c r="I188" s="8" t="n"/>
@@ -7478,8 +7475,8 @@
         <f>IF(C189="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E189" s="16" t="n"/>
-      <c r="F189" s="16" t="n"/>
+      <c r="E189" s="9" t="n"/>
+      <c r="F189" s="9" t="n"/>
       <c r="G189" s="8" t="n"/>
       <c r="H189" s="8" t="n"/>
       <c r="I189" s="8" t="n"/>
@@ -7512,8 +7509,8 @@
         <f>IF(C190="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E190" s="16" t="n"/>
-      <c r="F190" s="16" t="n"/>
+      <c r="E190" s="9" t="n"/>
+      <c r="F190" s="9" t="n"/>
       <c r="G190" s="8" t="n"/>
       <c r="H190" s="8" t="n"/>
       <c r="I190" s="8" t="n"/>
@@ -7546,8 +7543,8 @@
         <f>IF(C191="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E191" s="16" t="n"/>
-      <c r="F191" s="16" t="n"/>
+      <c r="E191" s="9" t="n"/>
+      <c r="F191" s="9" t="n"/>
       <c r="G191" s="8" t="n"/>
       <c r="H191" s="8" t="n"/>
       <c r="I191" s="8" t="n"/>
@@ -7580,8 +7577,8 @@
         <f>IF(C192="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E192" s="16" t="n"/>
-      <c r="F192" s="16" t="n"/>
+      <c r="E192" s="9" t="n"/>
+      <c r="F192" s="9" t="n"/>
       <c r="G192" s="8" t="n"/>
       <c r="H192" s="8" t="n"/>
       <c r="I192" s="8" t="n"/>
@@ -7614,8 +7611,8 @@
         <f>IF(C193="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E193" s="16" t="n"/>
-      <c r="F193" s="16" t="n"/>
+      <c r="E193" s="9" t="n"/>
+      <c r="F193" s="9" t="n"/>
       <c r="G193" s="8" t="n"/>
       <c r="H193" s="8" t="n"/>
       <c r="I193" s="8" t="n"/>
@@ -7648,8 +7645,8 @@
         <f>IF(C194="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E194" s="16" t="n"/>
-      <c r="F194" s="16" t="n"/>
+      <c r="E194" s="9" t="n"/>
+      <c r="F194" s="9" t="n"/>
       <c r="G194" s="8" t="n"/>
       <c r="H194" s="8" t="n"/>
       <c r="I194" s="8" t="n"/>
@@ -7682,8 +7679,8 @@
         <f>IF(C195="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E195" s="16" t="n"/>
-      <c r="F195" s="16" t="n"/>
+      <c r="E195" s="9" t="n"/>
+      <c r="F195" s="9" t="n"/>
       <c r="G195" s="8" t="n"/>
       <c r="H195" s="8" t="n"/>
       <c r="I195" s="8" t="n"/>
@@ -7716,8 +7713,8 @@
         <f>IF(C196="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E196" s="16" t="n"/>
-      <c r="F196" s="16" t="n"/>
+      <c r="E196" s="9" t="n"/>
+      <c r="F196" s="9" t="n"/>
       <c r="G196" s="8" t="n"/>
       <c r="H196" s="8" t="n"/>
       <c r="I196" s="8" t="n"/>
@@ -7750,8 +7747,8 @@
         <f>IF(C197="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E197" s="16" t="n"/>
-      <c r="F197" s="16" t="n"/>
+      <c r="E197" s="9" t="n"/>
+      <c r="F197" s="9" t="n"/>
       <c r="G197" s="8" t="n"/>
       <c r="H197" s="8" t="n"/>
       <c r="I197" s="8" t="n"/>
@@ -7784,8 +7781,8 @@
         <f>IF(C198="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E198" s="16" t="n"/>
-      <c r="F198" s="16" t="n"/>
+      <c r="E198" s="9" t="n"/>
+      <c r="F198" s="9" t="n"/>
       <c r="G198" s="8" t="n"/>
       <c r="H198" s="8" t="n"/>
       <c r="I198" s="8" t="n"/>
@@ -7818,8 +7815,8 @@
         <f>IF(C199="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E199" s="16" t="n"/>
-      <c r="F199" s="16" t="n"/>
+      <c r="E199" s="9" t="n"/>
+      <c r="F199" s="9" t="n"/>
       <c r="G199" s="8" t="n"/>
       <c r="H199" s="8" t="n"/>
       <c r="I199" s="8" t="n"/>
@@ -7852,8 +7849,8 @@
         <f>IF(C200="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E200" s="16" t="n"/>
-      <c r="F200" s="16" t="n"/>
+      <c r="E200" s="9" t="n"/>
+      <c r="F200" s="9" t="n"/>
       <c r="G200" s="8" t="n"/>
       <c r="H200" s="8" t="n"/>
       <c r="I200" s="8" t="n"/>
@@ -7886,8 +7883,8 @@
         <f>IF(C201="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E201" s="16" t="n"/>
-      <c r="F201" s="16" t="n"/>
+      <c r="E201" s="9" t="n"/>
+      <c r="F201" s="9" t="n"/>
       <c r="G201" s="8" t="n"/>
       <c r="H201" s="8" t="n"/>
       <c r="I201" s="8" t="n"/>
@@ -7920,8 +7917,8 @@
         <f>IF(C202="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E202" s="16" t="n"/>
-      <c r="F202" s="16" t="n"/>
+      <c r="E202" s="9" t="n"/>
+      <c r="F202" s="9" t="n"/>
       <c r="G202" s="8" t="n"/>
       <c r="H202" s="8" t="n"/>
       <c r="I202" s="8" t="n"/>
@@ -7954,8 +7951,8 @@
         <f>IF(C203="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E203" s="16" t="n"/>
-      <c r="F203" s="16" t="n"/>
+      <c r="E203" s="9" t="n"/>
+      <c r="F203" s="9" t="n"/>
       <c r="G203" s="8" t="n"/>
       <c r="H203" s="8" t="n"/>
       <c r="I203" s="8" t="n"/>
@@ -7988,8 +7985,8 @@
         <f>IF(C204="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E204" s="16" t="n"/>
-      <c r="F204" s="16" t="n"/>
+      <c r="E204" s="9" t="n"/>
+      <c r="F204" s="9" t="n"/>
       <c r="G204" s="8" t="n"/>
       <c r="H204" s="8" t="n"/>
       <c r="I204" s="8" t="n"/>
@@ -8022,8 +8019,8 @@
         <f>IF(C205="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E205" s="16" t="n"/>
-      <c r="F205" s="16" t="n"/>
+      <c r="E205" s="9" t="n"/>
+      <c r="F205" s="9" t="n"/>
       <c r="G205" s="8" t="n"/>
       <c r="H205" s="8" t="n"/>
       <c r="I205" s="8" t="n"/>
@@ -8056,8 +8053,8 @@
         <f>IF(C206="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E206" s="16" t="n"/>
-      <c r="F206" s="16" t="n"/>
+      <c r="E206" s="9" t="n"/>
+      <c r="F206" s="9" t="n"/>
       <c r="G206" s="8" t="n"/>
       <c r="H206" s="8" t="n"/>
       <c r="I206" s="8" t="n"/>
@@ -8090,8 +8087,8 @@
         <f>IF(C207="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E207" s="16" t="n"/>
-      <c r="F207" s="16" t="n"/>
+      <c r="E207" s="9" t="n"/>
+      <c r="F207" s="9" t="n"/>
       <c r="G207" s="8" t="n"/>
       <c r="H207" s="8" t="n"/>
       <c r="I207" s="8" t="n"/>
@@ -8124,8 +8121,8 @@
         <f>IF(C208="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E208" s="16" t="n"/>
-      <c r="F208" s="16" t="n"/>
+      <c r="E208" s="9" t="n"/>
+      <c r="F208" s="9" t="n"/>
       <c r="G208" s="8" t="n"/>
       <c r="H208" s="8" t="n"/>
       <c r="I208" s="8" t="n"/>
@@ -8158,8 +8155,8 @@
         <f>IF(C209="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E209" s="16" t="n"/>
-      <c r="F209" s="16" t="n"/>
+      <c r="E209" s="9" t="n"/>
+      <c r="F209" s="9" t="n"/>
       <c r="G209" s="8" t="n"/>
       <c r="H209" s="8" t="n"/>
       <c r="I209" s="8" t="n"/>
@@ -8192,8 +8189,8 @@
         <f>IF(C210="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E210" s="16" t="n"/>
-      <c r="F210" s="16" t="n"/>
+      <c r="E210" s="9" t="n"/>
+      <c r="F210" s="9" t="n"/>
       <c r="G210" s="8" t="n"/>
       <c r="H210" s="8" t="n"/>
       <c r="I210" s="8" t="n"/>
@@ -8226,8 +8223,8 @@
         <f>IF(C211="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E211" s="16" t="n"/>
-      <c r="F211" s="16" t="n"/>
+      <c r="E211" s="9" t="n"/>
+      <c r="F211" s="9" t="n"/>
       <c r="G211" s="8" t="n"/>
       <c r="H211" s="8" t="n"/>
       <c r="I211" s="8" t="n"/>
@@ -8260,8 +8257,8 @@
         <f>IF(C212="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E212" s="16" t="n"/>
-      <c r="F212" s="16" t="n"/>
+      <c r="E212" s="9" t="n"/>
+      <c r="F212" s="9" t="n"/>
       <c r="G212" s="8" t="n"/>
       <c r="H212" s="8" t="n"/>
       <c r="I212" s="8" t="n"/>
@@ -8294,8 +8291,8 @@
         <f>IF(C213="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E213" s="16" t="n"/>
-      <c r="F213" s="16" t="n"/>
+      <c r="E213" s="9" t="n"/>
+      <c r="F213" s="9" t="n"/>
       <c r="G213" s="8" t="n"/>
       <c r="H213" s="8" t="n"/>
       <c r="I213" s="8" t="n"/>
@@ -8328,8 +8325,8 @@
         <f>IF(C214="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E214" s="16" t="n"/>
-      <c r="F214" s="16" t="n"/>
+      <c r="E214" s="9" t="n"/>
+      <c r="F214" s="9" t="n"/>
       <c r="G214" s="8" t="n"/>
       <c r="H214" s="8" t="n"/>
       <c r="I214" s="8" t="n"/>
@@ -8362,8 +8359,8 @@
         <f>IF(C215="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E215" s="16" t="n"/>
-      <c r="F215" s="16" t="n"/>
+      <c r="E215" s="9" t="n"/>
+      <c r="F215" s="9" t="n"/>
       <c r="G215" s="8" t="n"/>
       <c r="H215" s="8" t="n"/>
       <c r="I215" s="8" t="n"/>
@@ -8396,8 +8393,8 @@
         <f>IF(C216="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E216" s="16" t="n"/>
-      <c r="F216" s="16" t="n"/>
+      <c r="E216" s="9" t="n"/>
+      <c r="F216" s="9" t="n"/>
       <c r="G216" s="8" t="n"/>
       <c r="H216" s="8" t="n"/>
       <c r="I216" s="8" t="n"/>
@@ -8430,8 +8427,8 @@
         <f>IF(C217="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E217" s="16" t="n"/>
-      <c r="F217" s="16" t="n"/>
+      <c r="E217" s="9" t="n"/>
+      <c r="F217" s="9" t="n"/>
       <c r="G217" s="8" t="n"/>
       <c r="H217" s="8" t="n"/>
       <c r="I217" s="8" t="n"/>
@@ -8464,8 +8461,8 @@
         <f>IF(C218="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E218" s="16" t="n"/>
-      <c r="F218" s="16" t="n"/>
+      <c r="E218" s="9" t="n"/>
+      <c r="F218" s="9" t="n"/>
       <c r="G218" s="8" t="n"/>
       <c r="H218" s="8" t="n"/>
       <c r="I218" s="8" t="n"/>
@@ -8498,8 +8495,8 @@
         <f>IF(C219="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E219" s="16" t="n"/>
-      <c r="F219" s="16" t="n"/>
+      <c r="E219" s="9" t="n"/>
+      <c r="F219" s="9" t="n"/>
       <c r="G219" s="8" t="n"/>
       <c r="H219" s="8" t="n"/>
       <c r="I219" s="8" t="n"/>
@@ -8532,8 +8529,8 @@
         <f>IF(C220="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E220" s="16" t="n"/>
-      <c r="F220" s="16" t="n"/>
+      <c r="E220" s="9" t="n"/>
+      <c r="F220" s="9" t="n"/>
       <c r="G220" s="8" t="n"/>
       <c r="H220" s="8" t="n"/>
       <c r="I220" s="8" t="n"/>
@@ -8566,8 +8563,8 @@
         <f>IF(C221="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E221" s="16" t="n"/>
-      <c r="F221" s="16" t="n"/>
+      <c r="E221" s="9" t="n"/>
+      <c r="F221" s="9" t="n"/>
       <c r="G221" s="8" t="n"/>
       <c r="H221" s="8" t="n"/>
       <c r="I221" s="8" t="n"/>
@@ -8600,8 +8597,8 @@
         <f>IF(C222="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E222" s="16" t="n"/>
-      <c r="F222" s="16" t="n"/>
+      <c r="E222" s="9" t="n"/>
+      <c r="F222" s="9" t="n"/>
       <c r="G222" s="8" t="n"/>
       <c r="H222" s="8" t="n"/>
       <c r="I222" s="8" t="n"/>
@@ -8634,8 +8631,8 @@
         <f>IF(C223="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E223" s="16" t="n"/>
-      <c r="F223" s="16" t="n"/>
+      <c r="E223" s="9" t="n"/>
+      <c r="F223" s="9" t="n"/>
       <c r="G223" s="8" t="n"/>
       <c r="H223" s="8" t="n"/>
       <c r="I223" s="8" t="n"/>
@@ -8668,8 +8665,8 @@
         <f>IF(C224="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E224" s="16" t="n"/>
-      <c r="F224" s="16" t="n"/>
+      <c r="E224" s="9" t="n"/>
+      <c r="F224" s="9" t="n"/>
       <c r="G224" s="8" t="n"/>
       <c r="H224" s="8" t="n"/>
       <c r="I224" s="8" t="n"/>
@@ -8702,8 +8699,8 @@
         <f>IF(C225="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E225" s="16" t="n"/>
-      <c r="F225" s="16" t="n"/>
+      <c r="E225" s="9" t="n"/>
+      <c r="F225" s="9" t="n"/>
       <c r="G225" s="8" t="n"/>
       <c r="H225" s="8" t="n"/>
       <c r="I225" s="8" t="n"/>
@@ -8736,8 +8733,8 @@
         <f>IF(C226="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E226" s="16" t="n"/>
-      <c r="F226" s="16" t="n"/>
+      <c r="E226" s="9" t="n"/>
+      <c r="F226" s="9" t="n"/>
       <c r="G226" s="8" t="n"/>
       <c r="H226" s="8" t="n"/>
       <c r="I226" s="8" t="n"/>
@@ -8770,8 +8767,8 @@
         <f>IF(C227="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E227" s="16" t="n"/>
-      <c r="F227" s="16" t="n"/>
+      <c r="E227" s="9" t="n"/>
+      <c r="F227" s="9" t="n"/>
       <c r="G227" s="8" t="n"/>
       <c r="H227" s="8" t="n"/>
       <c r="I227" s="8" t="n"/>
@@ -8804,8 +8801,8 @@
         <f>IF(C228="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E228" s="16" t="n"/>
-      <c r="F228" s="16" t="n"/>
+      <c r="E228" s="9" t="n"/>
+      <c r="F228" s="9" t="n"/>
       <c r="G228" s="8" t="n"/>
       <c r="H228" s="8" t="n"/>
       <c r="I228" s="8" t="n"/>
@@ -8838,8 +8835,8 @@
         <f>IF(C229="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E229" s="16" t="n"/>
-      <c r="F229" s="16" t="n"/>
+      <c r="E229" s="9" t="n"/>
+      <c r="F229" s="9" t="n"/>
       <c r="G229" s="8" t="n"/>
       <c r="H229" s="8" t="n"/>
       <c r="I229" s="8" t="n"/>
@@ -8872,8 +8869,8 @@
         <f>IF(C230="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E230" s="16" t="n"/>
-      <c r="F230" s="16" t="n"/>
+      <c r="E230" s="9" t="n"/>
+      <c r="F230" s="9" t="n"/>
       <c r="G230" s="8" t="n"/>
       <c r="H230" s="8" t="n"/>
       <c r="I230" s="8" t="n"/>
@@ -8906,8 +8903,8 @@
         <f>IF(C231="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E231" s="16" t="n"/>
-      <c r="F231" s="16" t="n"/>
+      <c r="E231" s="9" t="n"/>
+      <c r="F231" s="9" t="n"/>
       <c r="G231" s="8" t="n"/>
       <c r="H231" s="8" t="n"/>
       <c r="I231" s="8" t="n"/>
@@ -8940,8 +8937,8 @@
         <f>IF(C232="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E232" s="16" t="n"/>
-      <c r="F232" s="16" t="n"/>
+      <c r="E232" s="9" t="n"/>
+      <c r="F232" s="9" t="n"/>
       <c r="G232" s="8" t="n"/>
       <c r="H232" s="8" t="n"/>
       <c r="I232" s="8" t="n"/>
@@ -8974,8 +8971,8 @@
         <f>IF(C233="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E233" s="16" t="n"/>
-      <c r="F233" s="16" t="n"/>
+      <c r="E233" s="9" t="n"/>
+      <c r="F233" s="9" t="n"/>
       <c r="G233" s="8" t="n"/>
       <c r="H233" s="8" t="n"/>
       <c r="I233" s="8" t="n"/>
@@ -9008,8 +9005,8 @@
         <f>IF(C234="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E234" s="16" t="n"/>
-      <c r="F234" s="16" t="n"/>
+      <c r="E234" s="9" t="n"/>
+      <c r="F234" s="9" t="n"/>
       <c r="G234" s="8" t="n"/>
       <c r="H234" s="8" t="n"/>
       <c r="I234" s="8" t="n"/>
@@ -9042,8 +9039,8 @@
         <f>IF(C235="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E235" s="16" t="n"/>
-      <c r="F235" s="16" t="n"/>
+      <c r="E235" s="9" t="n"/>
+      <c r="F235" s="9" t="n"/>
       <c r="G235" s="8" t="n"/>
       <c r="H235" s="8" t="n"/>
       <c r="I235" s="8" t="n"/>
@@ -9076,8 +9073,8 @@
         <f>IF(C236="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E236" s="16" t="n"/>
-      <c r="F236" s="16" t="n"/>
+      <c r="E236" s="9" t="n"/>
+      <c r="F236" s="9" t="n"/>
       <c r="G236" s="8" t="n"/>
       <c r="H236" s="8" t="n"/>
       <c r="I236" s="8" t="n"/>
@@ -9110,8 +9107,8 @@
         <f>IF(C237="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E237" s="16" t="n"/>
-      <c r="F237" s="16" t="n"/>
+      <c r="E237" s="9" t="n"/>
+      <c r="F237" s="9" t="n"/>
       <c r="G237" s="8" t="n"/>
       <c r="H237" s="8" t="n"/>
       <c r="I237" s="8" t="n"/>
@@ -9144,8 +9141,8 @@
         <f>IF(C238="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E238" s="16" t="n"/>
-      <c r="F238" s="16" t="n"/>
+      <c r="E238" s="9" t="n"/>
+      <c r="F238" s="9" t="n"/>
       <c r="G238" s="8" t="n"/>
       <c r="H238" s="8" t="n"/>
       <c r="I238" s="8" t="n"/>
@@ -9178,8 +9175,8 @@
         <f>IF(C239="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E239" s="16" t="n"/>
-      <c r="F239" s="16" t="n"/>
+      <c r="E239" s="9" t="n"/>
+      <c r="F239" s="9" t="n"/>
       <c r="G239" s="8" t="n"/>
       <c r="H239" s="8" t="n"/>
       <c r="I239" s="8" t="n"/>
@@ -9212,8 +9209,8 @@
         <f>IF(C240="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E240" s="16" t="n"/>
-      <c r="F240" s="16" t="n"/>
+      <c r="E240" s="9" t="n"/>
+      <c r="F240" s="9" t="n"/>
       <c r="G240" s="8" t="n"/>
       <c r="H240" s="8" t="n"/>
       <c r="I240" s="8" t="n"/>
@@ -9246,8 +9243,8 @@
         <f>IF(C241="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E241" s="16" t="n"/>
-      <c r="F241" s="16" t="n"/>
+      <c r="E241" s="9" t="n"/>
+      <c r="F241" s="9" t="n"/>
       <c r="G241" s="8" t="n"/>
       <c r="H241" s="8" t="n"/>
       <c r="I241" s="8" t="n"/>
@@ -9280,8 +9277,8 @@
         <f>IF(C242="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E242" s="16" t="n"/>
-      <c r="F242" s="16" t="n"/>
+      <c r="E242" s="9" t="n"/>
+      <c r="F242" s="9" t="n"/>
       <c r="G242" s="8" t="n"/>
       <c r="H242" s="8" t="n"/>
       <c r="I242" s="8" t="n"/>
@@ -9314,8 +9311,8 @@
         <f>IF(C243="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E243" s="16" t="n"/>
-      <c r="F243" s="16" t="n"/>
+      <c r="E243" s="9" t="n"/>
+      <c r="F243" s="9" t="n"/>
       <c r="G243" s="8" t="n"/>
       <c r="H243" s="8" t="n"/>
       <c r="I243" s="8" t="n"/>
@@ -9348,8 +9345,8 @@
         <f>IF(C244="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E244" s="16" t="n"/>
-      <c r="F244" s="16" t="n"/>
+      <c r="E244" s="9" t="n"/>
+      <c r="F244" s="9" t="n"/>
       <c r="G244" s="8" t="n"/>
       <c r="H244" s="8" t="n"/>
       <c r="I244" s="8" t="n"/>
@@ -9382,8 +9379,8 @@
         <f>IF(C245="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E245" s="16" t="n"/>
-      <c r="F245" s="16" t="n"/>
+      <c r="E245" s="9" t="n"/>
+      <c r="F245" s="9" t="n"/>
       <c r="G245" s="8" t="n"/>
       <c r="H245" s="8" t="n"/>
       <c r="I245" s="8" t="n"/>
@@ -9416,8 +9413,8 @@
         <f>IF(C246="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E246" s="16" t="n"/>
-      <c r="F246" s="16" t="n"/>
+      <c r="E246" s="9" t="n"/>
+      <c r="F246" s="9" t="n"/>
       <c r="G246" s="8" t="n"/>
       <c r="H246" s="8" t="n"/>
       <c r="I246" s="8" t="n"/>
@@ -9450,8 +9447,8 @@
         <f>IF(C247="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E247" s="16" t="n"/>
-      <c r="F247" s="16" t="n"/>
+      <c r="E247" s="9" t="n"/>
+      <c r="F247" s="9" t="n"/>
       <c r="G247" s="8" t="n"/>
       <c r="H247" s="8" t="n"/>
       <c r="I247" s="8" t="n"/>
@@ -9484,8 +9481,8 @@
         <f>IF(C248="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E248" s="16" t="n"/>
-      <c r="F248" s="16" t="n"/>
+      <c r="E248" s="9" t="n"/>
+      <c r="F248" s="9" t="n"/>
       <c r="G248" s="8" t="n"/>
       <c r="H248" s="8" t="n"/>
       <c r="I248" s="8" t="n"/>
@@ -9518,8 +9515,8 @@
         <f>IF(C249="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E249" s="16" t="n"/>
-      <c r="F249" s="16" t="n"/>
+      <c r="E249" s="9" t="n"/>
+      <c r="F249" s="9" t="n"/>
       <c r="G249" s="8" t="n"/>
       <c r="H249" s="8" t="n"/>
       <c r="I249" s="8" t="n"/>
@@ -9552,8 +9549,8 @@
         <f>IF(C250="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E250" s="16" t="n"/>
-      <c r="F250" s="16" t="n"/>
+      <c r="E250" s="9" t="n"/>
+      <c r="F250" s="9" t="n"/>
       <c r="G250" s="8" t="n"/>
       <c r="H250" s="8" t="n"/>
       <c r="I250" s="8" t="n"/>
@@ -9586,8 +9583,8 @@
         <f>IF(C251="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E251" s="16" t="n"/>
-      <c r="F251" s="16" t="n"/>
+      <c r="E251" s="9" t="n"/>
+      <c r="F251" s="9" t="n"/>
       <c r="G251" s="8" t="n"/>
       <c r="H251" s="8" t="n"/>
       <c r="I251" s="8" t="n"/>
@@ -9620,8 +9617,8 @@
         <f>IF(C252="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E252" s="16" t="n"/>
-      <c r="F252" s="16" t="n"/>
+      <c r="E252" s="9" t="n"/>
+      <c r="F252" s="9" t="n"/>
       <c r="G252" s="8" t="n"/>
       <c r="H252" s="8" t="n"/>
       <c r="I252" s="8" t="n"/>
@@ -9654,8 +9651,8 @@
         <f>IF(C253="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E253" s="16" t="n"/>
-      <c r="F253" s="16" t="n"/>
+      <c r="E253" s="9" t="n"/>
+      <c r="F253" s="9" t="n"/>
       <c r="G253" s="8" t="n"/>
       <c r="H253" s="8" t="n"/>
       <c r="I253" s="8" t="n"/>
@@ -9688,8 +9685,8 @@
         <f>IF(C254="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E254" s="16" t="n"/>
-      <c r="F254" s="16" t="n"/>
+      <c r="E254" s="9" t="n"/>
+      <c r="F254" s="9" t="n"/>
       <c r="G254" s="8" t="n"/>
       <c r="H254" s="8" t="n"/>
       <c r="I254" s="8" t="n"/>
@@ -9722,8 +9719,8 @@
         <f>IF(C255="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E255" s="16" t="n"/>
-      <c r="F255" s="16" t="n"/>
+      <c r="E255" s="9" t="n"/>
+      <c r="F255" s="9" t="n"/>
       <c r="G255" s="8" t="n"/>
       <c r="H255" s="8" t="n"/>
       <c r="I255" s="8" t="n"/>
@@ -9756,8 +9753,8 @@
         <f>IF(C256="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E256" s="16" t="n"/>
-      <c r="F256" s="16" t="n"/>
+      <c r="E256" s="9" t="n"/>
+      <c r="F256" s="9" t="n"/>
       <c r="G256" s="8" t="n"/>
       <c r="H256" s="8" t="n"/>
       <c r="I256" s="8" t="n"/>
@@ -9790,8 +9787,8 @@
         <f>IF(C257="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E257" s="16" t="n"/>
-      <c r="F257" s="16" t="n"/>
+      <c r="E257" s="9" t="n"/>
+      <c r="F257" s="9" t="n"/>
       <c r="G257" s="8" t="n"/>
       <c r="H257" s="8" t="n"/>
       <c r="I257" s="8" t="n"/>
@@ -9824,8 +9821,8 @@
         <f>IF(C258="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E258" s="16" t="n"/>
-      <c r="F258" s="16" t="n"/>
+      <c r="E258" s="9" t="n"/>
+      <c r="F258" s="9" t="n"/>
       <c r="G258" s="8" t="n"/>
       <c r="H258" s="8" t="n"/>
       <c r="I258" s="8" t="n"/>
@@ -9858,8 +9855,8 @@
         <f>IF(C259="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E259" s="16" t="n"/>
-      <c r="F259" s="16" t="n"/>
+      <c r="E259" s="9" t="n"/>
+      <c r="F259" s="9" t="n"/>
       <c r="G259" s="8" t="n"/>
       <c r="H259" s="8" t="n"/>
       <c r="I259" s="8" t="n"/>
@@ -9892,8 +9889,8 @@
         <f>IF(C260="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E260" s="16" t="n"/>
-      <c r="F260" s="16" t="n"/>
+      <c r="E260" s="9" t="n"/>
+      <c r="F260" s="9" t="n"/>
       <c r="G260" s="8" t="n"/>
       <c r="H260" s="8" t="n"/>
       <c r="I260" s="8" t="n"/>
@@ -9926,8 +9923,8 @@
         <f>IF(C261="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E261" s="16" t="n"/>
-      <c r="F261" s="16" t="n"/>
+      <c r="E261" s="9" t="n"/>
+      <c r="F261" s="9" t="n"/>
       <c r="G261" s="8" t="n"/>
       <c r="H261" s="8" t="n"/>
       <c r="I261" s="8" t="n"/>
@@ -9960,8 +9957,8 @@
         <f>IF(C262="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E262" s="16" t="n"/>
-      <c r="F262" s="16" t="n"/>
+      <c r="E262" s="9" t="n"/>
+      <c r="F262" s="9" t="n"/>
       <c r="G262" s="8" t="n"/>
       <c r="H262" s="8" t="n"/>
       <c r="I262" s="8" t="n"/>
@@ -9994,8 +9991,8 @@
         <f>IF(C263="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E263" s="16" t="n"/>
-      <c r="F263" s="16" t="n"/>
+      <c r="E263" s="9" t="n"/>
+      <c r="F263" s="9" t="n"/>
       <c r="G263" s="8" t="n"/>
       <c r="H263" s="8" t="n"/>
       <c r="I263" s="8" t="n"/>
@@ -10028,8 +10025,8 @@
         <f>IF(C264="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E264" s="16" t="n"/>
-      <c r="F264" s="16" t="n"/>
+      <c r="E264" s="9" t="n"/>
+      <c r="F264" s="9" t="n"/>
       <c r="G264" s="8" t="n"/>
       <c r="H264" s="8" t="n"/>
       <c r="I264" s="8" t="n"/>
@@ -10062,8 +10059,8 @@
         <f>IF(C265="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E265" s="16" t="n"/>
-      <c r="F265" s="16" t="n"/>
+      <c r="E265" s="9" t="n"/>
+      <c r="F265" s="9" t="n"/>
       <c r="G265" s="8" t="n"/>
       <c r="H265" s="8" t="n"/>
       <c r="I265" s="8" t="n"/>
@@ -10096,8 +10093,8 @@
         <f>IF(C266="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E266" s="16" t="n"/>
-      <c r="F266" s="16" t="n"/>
+      <c r="E266" s="9" t="n"/>
+      <c r="F266" s="9" t="n"/>
       <c r="G266" s="8" t="n"/>
       <c r="H266" s="8" t="n"/>
       <c r="I266" s="8" t="n"/>
@@ -10130,8 +10127,8 @@
         <f>IF(C267="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E267" s="16" t="n"/>
-      <c r="F267" s="16" t="n"/>
+      <c r="E267" s="9" t="n"/>
+      <c r="F267" s="9" t="n"/>
       <c r="G267" s="8" t="n"/>
       <c r="H267" s="8" t="n"/>
       <c r="I267" s="8" t="n"/>
@@ -10164,8 +10161,8 @@
         <f>IF(C268="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E268" s="16" t="n"/>
-      <c r="F268" s="16" t="n"/>
+      <c r="E268" s="9" t="n"/>
+      <c r="F268" s="9" t="n"/>
       <c r="G268" s="8" t="n"/>
       <c r="H268" s="8" t="n"/>
       <c r="I268" s="8" t="n"/>
@@ -10198,8 +10195,8 @@
         <f>IF(C269="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E269" s="16" t="n"/>
-      <c r="F269" s="16" t="n"/>
+      <c r="E269" s="9" t="n"/>
+      <c r="F269" s="9" t="n"/>
       <c r="G269" s="8" t="n"/>
       <c r="H269" s="8" t="n"/>
       <c r="I269" s="8" t="n"/>
@@ -10232,8 +10229,8 @@
         <f>IF(C270="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E270" s="16" t="n"/>
-      <c r="F270" s="16" t="n"/>
+      <c r="E270" s="9" t="n"/>
+      <c r="F270" s="9" t="n"/>
       <c r="G270" s="8" t="n"/>
       <c r="H270" s="8" t="n"/>
       <c r="I270" s="8" t="n"/>
@@ -10266,8 +10263,8 @@
         <f>IF(C271="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E271" s="16" t="n"/>
-      <c r="F271" s="16" t="n"/>
+      <c r="E271" s="9" t="n"/>
+      <c r="F271" s="9" t="n"/>
       <c r="G271" s="8" t="n"/>
       <c r="H271" s="8" t="n"/>
       <c r="I271" s="8" t="n"/>
@@ -10300,8 +10297,8 @@
         <f>IF(C272="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E272" s="16" t="n"/>
-      <c r="F272" s="16" t="n"/>
+      <c r="E272" s="9" t="n"/>
+      <c r="F272" s="9" t="n"/>
       <c r="G272" s="8" t="n"/>
       <c r="H272" s="8" t="n"/>
       <c r="I272" s="8" t="n"/>
@@ -10334,8 +10331,8 @@
         <f>IF(C273="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E273" s="16" t="n"/>
-      <c r="F273" s="16" t="n"/>
+      <c r="E273" s="9" t="n"/>
+      <c r="F273" s="9" t="n"/>
       <c r="G273" s="8" t="n"/>
       <c r="H273" s="8" t="n"/>
       <c r="I273" s="8" t="n"/>
@@ -10368,8 +10365,8 @@
         <f>IF(C274="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E274" s="16" t="n"/>
-      <c r="F274" s="16" t="n"/>
+      <c r="E274" s="9" t="n"/>
+      <c r="F274" s="9" t="n"/>
       <c r="G274" s="8" t="n"/>
       <c r="H274" s="8" t="n"/>
       <c r="I274" s="8" t="n"/>
@@ -10402,8 +10399,8 @@
         <f>IF(C275="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E275" s="16" t="n"/>
-      <c r="F275" s="16" t="n"/>
+      <c r="E275" s="9" t="n"/>
+      <c r="F275" s="9" t="n"/>
       <c r="G275" s="8" t="n"/>
       <c r="H275" s="8" t="n"/>
       <c r="I275" s="8" t="n"/>
@@ -10436,8 +10433,8 @@
         <f>IF(C276="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E276" s="16" t="n"/>
-      <c r="F276" s="16" t="n"/>
+      <c r="E276" s="9" t="n"/>
+      <c r="F276" s="9" t="n"/>
       <c r="G276" s="8" t="n"/>
       <c r="H276" s="8" t="n"/>
       <c r="I276" s="8" t="n"/>
@@ -10470,8 +10467,8 @@
         <f>IF(C277="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E277" s="16" t="n"/>
-      <c r="F277" s="16" t="n"/>
+      <c r="E277" s="9" t="n"/>
+      <c r="F277" s="9" t="n"/>
       <c r="G277" s="8" t="n"/>
       <c r="H277" s="8" t="n"/>
       <c r="I277" s="8" t="n"/>
@@ -10504,8 +10501,8 @@
         <f>IF(C278="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E278" s="16" t="n"/>
-      <c r="F278" s="16" t="n"/>
+      <c r="E278" s="9" t="n"/>
+      <c r="F278" s="9" t="n"/>
       <c r="G278" s="8" t="n"/>
       <c r="H278" s="8" t="n"/>
       <c r="I278" s="8" t="n"/>
@@ -10538,8 +10535,8 @@
         <f>IF(C279="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E279" s="16" t="n"/>
-      <c r="F279" s="16" t="n"/>
+      <c r="E279" s="9" t="n"/>
+      <c r="F279" s="9" t="n"/>
       <c r="G279" s="8" t="n"/>
       <c r="H279" s="8" t="n"/>
       <c r="I279" s="8" t="n"/>
@@ -10572,8 +10569,8 @@
         <f>IF(C280="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E280" s="16" t="n"/>
-      <c r="F280" s="16" t="n"/>
+      <c r="E280" s="9" t="n"/>
+      <c r="F280" s="9" t="n"/>
       <c r="G280" s="8" t="n"/>
       <c r="H280" s="8" t="n"/>
       <c r="I280" s="8" t="n"/>
@@ -10606,8 +10603,8 @@
         <f>IF(C281="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E281" s="16" t="n"/>
-      <c r="F281" s="16" t="n"/>
+      <c r="E281" s="9" t="n"/>
+      <c r="F281" s="9" t="n"/>
       <c r="G281" s="8" t="n"/>
       <c r="H281" s="8" t="n"/>
       <c r="I281" s="8" t="n"/>
@@ -10640,8 +10637,8 @@
         <f>IF(C282="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E282" s="16" t="n"/>
-      <c r="F282" s="16" t="n"/>
+      <c r="E282" s="9" t="n"/>
+      <c r="F282" s="9" t="n"/>
       <c r="G282" s="8" t="n"/>
       <c r="H282" s="8" t="n"/>
       <c r="I282" s="8" t="n"/>
@@ -10674,8 +10671,8 @@
         <f>IF(C283="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E283" s="16" t="n"/>
-      <c r="F283" s="16" t="n"/>
+      <c r="E283" s="9" t="n"/>
+      <c r="F283" s="9" t="n"/>
       <c r="G283" s="8" t="n"/>
       <c r="H283" s="8" t="n"/>
       <c r="I283" s="8" t="n"/>
@@ -10708,8 +10705,8 @@
         <f>IF(C284="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E284" s="16" t="n"/>
-      <c r="F284" s="16" t="n"/>
+      <c r="E284" s="9" t="n"/>
+      <c r="F284" s="9" t="n"/>
       <c r="G284" s="8" t="n"/>
       <c r="H284" s="8" t="n"/>
       <c r="I284" s="8" t="n"/>
@@ -10742,8 +10739,8 @@
         <f>IF(C285="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E285" s="16" t="n"/>
-      <c r="F285" s="16" t="n"/>
+      <c r="E285" s="9" t="n"/>
+      <c r="F285" s="9" t="n"/>
       <c r="G285" s="8" t="n"/>
       <c r="H285" s="8" t="n"/>
       <c r="I285" s="8" t="n"/>
@@ -10776,8 +10773,8 @@
         <f>IF(C286="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E286" s="16" t="n"/>
-      <c r="F286" s="16" t="n"/>
+      <c r="E286" s="9" t="n"/>
+      <c r="F286" s="9" t="n"/>
       <c r="G286" s="8" t="n"/>
       <c r="H286" s="8" t="n"/>
       <c r="I286" s="8" t="n"/>
@@ -10810,8 +10807,8 @@
         <f>IF(C287="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E287" s="16" t="n"/>
-      <c r="F287" s="16" t="n"/>
+      <c r="E287" s="9" t="n"/>
+      <c r="F287" s="9" t="n"/>
       <c r="G287" s="8" t="n"/>
       <c r="H287" s="8" t="n"/>
       <c r="I287" s="8" t="n"/>
@@ -10844,8 +10841,8 @@
         <f>IF(C288="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E288" s="16" t="n"/>
-      <c r="F288" s="16" t="n"/>
+      <c r="E288" s="9" t="n"/>
+      <c r="F288" s="9" t="n"/>
       <c r="G288" s="8" t="n"/>
       <c r="H288" s="8" t="n"/>
       <c r="I288" s="8" t="n"/>
@@ -10878,8 +10875,8 @@
         <f>IF(C289="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E289" s="16" t="n"/>
-      <c r="F289" s="16" t="n"/>
+      <c r="E289" s="9" t="n"/>
+      <c r="F289" s="9" t="n"/>
       <c r="G289" s="8" t="n"/>
       <c r="H289" s="8" t="n"/>
       <c r="I289" s="8" t="n"/>
@@ -10912,8 +10909,8 @@
         <f>IF(C290="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E290" s="16" t="n"/>
-      <c r="F290" s="16" t="n"/>
+      <c r="E290" s="9" t="n"/>
+      <c r="F290" s="9" t="n"/>
       <c r="G290" s="8" t="n"/>
       <c r="H290" s="8" t="n"/>
       <c r="I290" s="8" t="n"/>
@@ -10946,8 +10943,8 @@
         <f>IF(C291="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E291" s="16" t="n"/>
-      <c r="F291" s="16" t="n"/>
+      <c r="E291" s="9" t="n"/>
+      <c r="F291" s="9" t="n"/>
       <c r="G291" s="8" t="n"/>
       <c r="H291" s="8" t="n"/>
       <c r="I291" s="8" t="n"/>
@@ -10980,8 +10977,8 @@
         <f>IF(C292="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E292" s="16" t="n"/>
-      <c r="F292" s="16" t="n"/>
+      <c r="E292" s="9" t="n"/>
+      <c r="F292" s="9" t="n"/>
       <c r="G292" s="8" t="n"/>
       <c r="H292" s="8" t="n"/>
       <c r="I292" s="8" t="n"/>
@@ -11014,8 +11011,8 @@
         <f>IF(C293="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E293" s="16" t="n"/>
-      <c r="F293" s="16" t="n"/>
+      <c r="E293" s="9" t="n"/>
+      <c r="F293" s="9" t="n"/>
       <c r="G293" s="8" t="n"/>
       <c r="H293" s="8" t="n"/>
       <c r="I293" s="8" t="n"/>
@@ -11048,8 +11045,8 @@
         <f>IF(C294="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E294" s="16" t="n"/>
-      <c r="F294" s="16" t="n"/>
+      <c r="E294" s="9" t="n"/>
+      <c r="F294" s="9" t="n"/>
       <c r="G294" s="8" t="n"/>
       <c r="H294" s="8" t="n"/>
       <c r="I294" s="8" t="n"/>
@@ -11082,8 +11079,8 @@
         <f>IF(C295="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E295" s="16" t="n"/>
-      <c r="F295" s="16" t="n"/>
+      <c r="E295" s="9" t="n"/>
+      <c r="F295" s="9" t="n"/>
       <c r="G295" s="8" t="n"/>
       <c r="H295" s="8" t="n"/>
       <c r="I295" s="8" t="n"/>
@@ -11116,8 +11113,8 @@
         <f>IF(C296="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E296" s="16" t="n"/>
-      <c r="F296" s="16" t="n"/>
+      <c r="E296" s="9" t="n"/>
+      <c r="F296" s="9" t="n"/>
       <c r="G296" s="8" t="n"/>
       <c r="H296" s="8" t="n"/>
       <c r="I296" s="8" t="n"/>
@@ -11150,8 +11147,8 @@
         <f>IF(C297="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E297" s="16" t="n"/>
-      <c r="F297" s="16" t="n"/>
+      <c r="E297" s="9" t="n"/>
+      <c r="F297" s="9" t="n"/>
       <c r="G297" s="8" t="n"/>
       <c r="H297" s="8" t="n"/>
       <c r="I297" s="8" t="n"/>
@@ -11184,8 +11181,8 @@
         <f>IF(C298="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E298" s="16" t="n"/>
-      <c r="F298" s="16" t="n"/>
+      <c r="E298" s="9" t="n"/>
+      <c r="F298" s="9" t="n"/>
       <c r="G298" s="8" t="n"/>
       <c r="H298" s="8" t="n"/>
       <c r="I298" s="8" t="n"/>
@@ -11218,8 +11215,8 @@
         <f>IF(C299="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E299" s="16" t="n"/>
-      <c r="F299" s="16" t="n"/>
+      <c r="E299" s="9" t="n"/>
+      <c r="F299" s="9" t="n"/>
       <c r="G299" s="8" t="n"/>
       <c r="H299" s="8" t="n"/>
       <c r="I299" s="8" t="n"/>
@@ -11252,8 +11249,8 @@
         <f>IF(C300="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E300" s="16" t="n"/>
-      <c r="F300" s="16" t="n"/>
+      <c r="E300" s="9" t="n"/>
+      <c r="F300" s="9" t="n"/>
       <c r="G300" s="8" t="n"/>
       <c r="H300" s="8" t="n"/>
       <c r="I300" s="8" t="n"/>
@@ -11286,8 +11283,8 @@
         <f>IF(C301="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E301" s="16" t="n"/>
-      <c r="F301" s="16" t="n"/>
+      <c r="E301" s="9" t="n"/>
+      <c r="F301" s="9" t="n"/>
       <c r="G301" s="8" t="n"/>
       <c r="H301" s="8" t="n"/>
       <c r="I301" s="8" t="n"/>
@@ -11320,8 +11317,8 @@
         <f>IF(C302="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E302" s="16" t="n"/>
-      <c r="F302" s="16" t="n"/>
+      <c r="E302" s="9" t="n"/>
+      <c r="F302" s="9" t="n"/>
       <c r="G302" s="8" t="n"/>
       <c r="H302" s="8" t="n"/>
       <c r="I302" s="8" t="n"/>
@@ -11354,8 +11351,8 @@
         <f>IF(C303="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E303" s="16" t="n"/>
-      <c r="F303" s="16" t="n"/>
+      <c r="E303" s="9" t="n"/>
+      <c r="F303" s="9" t="n"/>
       <c r="G303" s="8" t="n"/>
       <c r="H303" s="8" t="n"/>
       <c r="I303" s="8" t="n"/>
@@ -11388,8 +11385,8 @@
         <f>IF(C304="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E304" s="16" t="n"/>
-      <c r="F304" s="16" t="n"/>
+      <c r="E304" s="9" t="n"/>
+      <c r="F304" s="9" t="n"/>
       <c r="G304" s="8" t="n"/>
       <c r="H304" s="8" t="n"/>
       <c r="I304" s="8" t="n"/>
@@ -11422,8 +11419,8 @@
         <f>IF(C305="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E305" s="16" t="n"/>
-      <c r="F305" s="16" t="n"/>
+      <c r="E305" s="9" t="n"/>
+      <c r="F305" s="9" t="n"/>
       <c r="G305" s="8" t="n"/>
       <c r="H305" s="8" t="n"/>
       <c r="I305" s="8" t="n"/>
@@ -11456,8 +11453,8 @@
         <f>IF(C306="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E306" s="16" t="n"/>
-      <c r="F306" s="16" t="n"/>
+      <c r="E306" s="9" t="n"/>
+      <c r="F306" s="9" t="n"/>
       <c r="G306" s="8" t="n"/>
       <c r="H306" s="8" t="n"/>
       <c r="I306" s="8" t="n"/>
@@ -11490,8 +11487,8 @@
         <f>IF(C307="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E307" s="16" t="n"/>
-      <c r="F307" s="16" t="n"/>
+      <c r="E307" s="9" t="n"/>
+      <c r="F307" s="9" t="n"/>
       <c r="G307" s="8" t="n"/>
       <c r="H307" s="8" t="n"/>
       <c r="I307" s="8" t="n"/>
@@ -11524,8 +11521,8 @@
         <f>IF(C308="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E308" s="16" t="n"/>
-      <c r="F308" s="16" t="n"/>
+      <c r="E308" s="9" t="n"/>
+      <c r="F308" s="9" t="n"/>
       <c r="G308" s="8" t="n"/>
       <c r="H308" s="8" t="n"/>
       <c r="I308" s="8" t="n"/>
@@ -11558,8 +11555,8 @@
         <f>IF(C309="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E309" s="16" t="n"/>
-      <c r="F309" s="16" t="n"/>
+      <c r="E309" s="9" t="n"/>
+      <c r="F309" s="9" t="n"/>
       <c r="G309" s="8" t="n"/>
       <c r="H309" s="8" t="n"/>
       <c r="I309" s="8" t="n"/>
@@ -11592,8 +11589,8 @@
         <f>IF(C310="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E310" s="16" t="n"/>
-      <c r="F310" s="16" t="n"/>
+      <c r="E310" s="9" t="n"/>
+      <c r="F310" s="9" t="n"/>
       <c r="G310" s="8" t="n"/>
       <c r="H310" s="8" t="n"/>
       <c r="I310" s="8" t="n"/>
@@ -11626,8 +11623,8 @@
         <f>IF(C311="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E311" s="16" t="n"/>
-      <c r="F311" s="16" t="n"/>
+      <c r="E311" s="9" t="n"/>
+      <c r="F311" s="9" t="n"/>
       <c r="G311" s="8" t="n"/>
       <c r="H311" s="8" t="n"/>
       <c r="I311" s="8" t="n"/>
@@ -11660,8 +11657,8 @@
         <f>IF(C312="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E312" s="16" t="n"/>
-      <c r="F312" s="16" t="n"/>
+      <c r="E312" s="9" t="n"/>
+      <c r="F312" s="9" t="n"/>
       <c r="G312" s="8" t="n"/>
       <c r="H312" s="8" t="n"/>
       <c r="I312" s="8" t="n"/>
@@ -11694,8 +11691,8 @@
         <f>IF(C313="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E313" s="16" t="n"/>
-      <c r="F313" s="16" t="n"/>
+      <c r="E313" s="9" t="n"/>
+      <c r="F313" s="9" t="n"/>
       <c r="G313" s="8" t="n"/>
       <c r="H313" s="8" t="n"/>
       <c r="I313" s="8" t="n"/>
@@ -11728,8 +11725,8 @@
         <f>IF(C314="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E314" s="16" t="n"/>
-      <c r="F314" s="16" t="n"/>
+      <c r="E314" s="9" t="n"/>
+      <c r="F314" s="9" t="n"/>
       <c r="G314" s="8" t="n"/>
       <c r="H314" s="8" t="n"/>
       <c r="I314" s="8" t="n"/>
@@ -11762,8 +11759,8 @@
         <f>IF(C315="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E315" s="16" t="n"/>
-      <c r="F315" s="16" t="n"/>
+      <c r="E315" s="9" t="n"/>
+      <c r="F315" s="9" t="n"/>
       <c r="G315" s="8" t="n"/>
       <c r="H315" s="8" t="n"/>
       <c r="I315" s="8" t="n"/>
@@ -11796,8 +11793,8 @@
         <f>IF(C316="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E316" s="16" t="n"/>
-      <c r="F316" s="16" t="n"/>
+      <c r="E316" s="9" t="n"/>
+      <c r="F316" s="9" t="n"/>
       <c r="G316" s="8" t="n"/>
       <c r="H316" s="8" t="n"/>
       <c r="I316" s="8" t="n"/>
@@ -11830,8 +11827,8 @@
         <f>IF(C317="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E317" s="16" t="n"/>
-      <c r="F317" s="16" t="n"/>
+      <c r="E317" s="9" t="n"/>
+      <c r="F317" s="9" t="n"/>
       <c r="G317" s="8" t="n"/>
       <c r="H317" s="8" t="n"/>
       <c r="I317" s="8" t="n"/>
@@ -11864,8 +11861,8 @@
         <f>IF(C318="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E318" s="16" t="n"/>
-      <c r="F318" s="16" t="n"/>
+      <c r="E318" s="9" t="n"/>
+      <c r="F318" s="9" t="n"/>
       <c r="G318" s="8" t="n"/>
       <c r="H318" s="8" t="n"/>
       <c r="I318" s="8" t="n"/>
@@ -11898,8 +11895,8 @@
         <f>IF(C319="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E319" s="16" t="n"/>
-      <c r="F319" s="16" t="n"/>
+      <c r="E319" s="9" t="n"/>
+      <c r="F319" s="9" t="n"/>
       <c r="G319" s="8" t="n"/>
       <c r="H319" s="8" t="n"/>
       <c r="I319" s="8" t="n"/>
@@ -11932,8 +11929,8 @@
         <f>IF(C320="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E320" s="16" t="n"/>
-      <c r="F320" s="16" t="n"/>
+      <c r="E320" s="9" t="n"/>
+      <c r="F320" s="9" t="n"/>
       <c r="G320" s="8" t="n"/>
       <c r="H320" s="8" t="n"/>
       <c r="I320" s="8" t="n"/>
@@ -11966,8 +11963,8 @@
         <f>IF(C321="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E321" s="16" t="n"/>
-      <c r="F321" s="16" t="n"/>
+      <c r="E321" s="9" t="n"/>
+      <c r="F321" s="9" t="n"/>
       <c r="G321" s="8" t="n"/>
       <c r="H321" s="8" t="n"/>
       <c r="I321" s="8" t="n"/>
@@ -12000,8 +11997,8 @@
         <f>IF(C322="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E322" s="16" t="n"/>
-      <c r="F322" s="16" t="n"/>
+      <c r="E322" s="9" t="n"/>
+      <c r="F322" s="9" t="n"/>
       <c r="G322" s="8" t="n"/>
       <c r="H322" s="8" t="n"/>
       <c r="I322" s="8" t="n"/>
@@ -12034,8 +12031,8 @@
         <f>IF(C323="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E323" s="16" t="n"/>
-      <c r="F323" s="16" t="n"/>
+      <c r="E323" s="9" t="n"/>
+      <c r="F323" s="9" t="n"/>
       <c r="G323" s="8" t="n"/>
       <c r="H323" s="8" t="n"/>
       <c r="I323" s="8" t="n"/>
@@ -12068,8 +12065,8 @@
         <f>IF(C324="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E324" s="16" t="n"/>
-      <c r="F324" s="16" t="n"/>
+      <c r="E324" s="9" t="n"/>
+      <c r="F324" s="9" t="n"/>
       <c r="G324" s="8" t="n"/>
       <c r="H324" s="8" t="n"/>
       <c r="I324" s="8" t="n"/>
@@ -12102,8 +12099,8 @@
         <f>IF(C325="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E325" s="16" t="n"/>
-      <c r="F325" s="16" t="n"/>
+      <c r="E325" s="9" t="n"/>
+      <c r="F325" s="9" t="n"/>
       <c r="G325" s="8" t="n"/>
       <c r="H325" s="8" t="n"/>
       <c r="I325" s="8" t="n"/>
@@ -12136,8 +12133,8 @@
         <f>IF(C326="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E326" s="16" t="n"/>
-      <c r="F326" s="16" t="n"/>
+      <c r="E326" s="9" t="n"/>
+      <c r="F326" s="9" t="n"/>
       <c r="G326" s="8" t="n"/>
       <c r="H326" s="8" t="n"/>
       <c r="I326" s="8" t="n"/>
@@ -12170,8 +12167,8 @@
         <f>IF(C327="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E327" s="16" t="n"/>
-      <c r="F327" s="16" t="n"/>
+      <c r="E327" s="9" t="n"/>
+      <c r="F327" s="9" t="n"/>
       <c r="G327" s="8" t="n"/>
       <c r="H327" s="8" t="n"/>
       <c r="I327" s="8" t="n"/>
@@ -12204,8 +12201,8 @@
         <f>IF(C328="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E328" s="16" t="n"/>
-      <c r="F328" s="16" t="n"/>
+      <c r="E328" s="9" t="n"/>
+      <c r="F328" s="9" t="n"/>
       <c r="G328" s="8" t="n"/>
       <c r="H328" s="8" t="n"/>
       <c r="I328" s="8" t="n"/>
@@ -12238,8 +12235,8 @@
         <f>IF(C329="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E329" s="16" t="n"/>
-      <c r="F329" s="16" t="n"/>
+      <c r="E329" s="9" t="n"/>
+      <c r="F329" s="9" t="n"/>
       <c r="G329" s="8" t="n"/>
       <c r="H329" s="8" t="n"/>
       <c r="I329" s="8" t="n"/>
@@ -12272,8 +12269,8 @@
         <f>IF(C330="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E330" s="16" t="n"/>
-      <c r="F330" s="16" t="n"/>
+      <c r="E330" s="9" t="n"/>
+      <c r="F330" s="9" t="n"/>
       <c r="G330" s="8" t="n"/>
       <c r="H330" s="8" t="n"/>
       <c r="I330" s="8" t="n"/>
@@ -12306,8 +12303,8 @@
         <f>IF(C331="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E331" s="16" t="n"/>
-      <c r="F331" s="16" t="n"/>
+      <c r="E331" s="9" t="n"/>
+      <c r="F331" s="9" t="n"/>
       <c r="G331" s="8" t="n"/>
       <c r="H331" s="8" t="n"/>
       <c r="I331" s="8" t="n"/>
@@ -12340,8 +12337,8 @@
         <f>IF(C332="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E332" s="16" t="n"/>
-      <c r="F332" s="16" t="n"/>
+      <c r="E332" s="9" t="n"/>
+      <c r="F332" s="9" t="n"/>
       <c r="G332" s="8" t="n"/>
       <c r="H332" s="8" t="n"/>
       <c r="I332" s="8" t="n"/>
@@ -12374,8 +12371,8 @@
         <f>IF(C333="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E333" s="16" t="n"/>
-      <c r="F333" s="16" t="n"/>
+      <c r="E333" s="9" t="n"/>
+      <c r="F333" s="9" t="n"/>
       <c r="G333" s="8" t="n"/>
       <c r="H333" s="8" t="n"/>
       <c r="I333" s="8" t="n"/>
@@ -12408,8 +12405,8 @@
         <f>IF(C334="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E334" s="16" t="n"/>
-      <c r="F334" s="16" t="n"/>
+      <c r="E334" s="9" t="n"/>
+      <c r="F334" s="9" t="n"/>
       <c r="G334" s="8" t="n"/>
       <c r="H334" s="8" t="n"/>
       <c r="I334" s="8" t="n"/>
@@ -12442,8 +12439,8 @@
         <f>IF(C335="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E335" s="16" t="n"/>
-      <c r="F335" s="16" t="n"/>
+      <c r="E335" s="9" t="n"/>
+      <c r="F335" s="9" t="n"/>
       <c r="G335" s="8" t="n"/>
       <c r="H335" s="8" t="n"/>
       <c r="I335" s="8" t="n"/>
@@ -12476,8 +12473,8 @@
         <f>IF(C336="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E336" s="16" t="n"/>
-      <c r="F336" s="16" t="n"/>
+      <c r="E336" s="9" t="n"/>
+      <c r="F336" s="9" t="n"/>
       <c r="G336" s="8" t="n"/>
       <c r="H336" s="8" t="n"/>
       <c r="I336" s="8" t="n"/>
@@ -12510,8 +12507,8 @@
         <f>IF(C337="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E337" s="16" t="n"/>
-      <c r="F337" s="16" t="n"/>
+      <c r="E337" s="9" t="n"/>
+      <c r="F337" s="9" t="n"/>
       <c r="G337" s="8" t="n"/>
       <c r="H337" s="8" t="n"/>
       <c r="I337" s="8" t="n"/>
@@ -12544,8 +12541,8 @@
         <f>IF(C338="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E338" s="16" t="n"/>
-      <c r="F338" s="16" t="n"/>
+      <c r="E338" s="9" t="n"/>
+      <c r="F338" s="9" t="n"/>
       <c r="G338" s="8" t="n"/>
       <c r="H338" s="8" t="n"/>
       <c r="I338" s="8" t="n"/>
@@ -12578,8 +12575,8 @@
         <f>IF(C339="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E339" s="16" t="n"/>
-      <c r="F339" s="16" t="n"/>
+      <c r="E339" s="9" t="n"/>
+      <c r="F339" s="9" t="n"/>
       <c r="G339" s="8" t="n"/>
       <c r="H339" s="8" t="n"/>
       <c r="I339" s="8" t="n"/>
@@ -12612,8 +12609,8 @@
         <f>IF(C340="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E340" s="16" t="n"/>
-      <c r="F340" s="16" t="n"/>
+      <c r="E340" s="9" t="n"/>
+      <c r="F340" s="9" t="n"/>
       <c r="G340" s="8" t="n"/>
       <c r="H340" s="8" t="n"/>
       <c r="I340" s="8" t="n"/>
@@ -12646,8 +12643,8 @@
         <f>IF(C341="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E341" s="16" t="n"/>
-      <c r="F341" s="16" t="n"/>
+      <c r="E341" s="9" t="n"/>
+      <c r="F341" s="9" t="n"/>
       <c r="G341" s="8" t="n"/>
       <c r="H341" s="8" t="n"/>
       <c r="I341" s="8" t="n"/>
@@ -12680,8 +12677,8 @@
         <f>IF(C342="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E342" s="16" t="n"/>
-      <c r="F342" s="16" t="n"/>
+      <c r="E342" s="9" t="n"/>
+      <c r="F342" s="9" t="n"/>
       <c r="G342" s="8" t="n"/>
       <c r="H342" s="8" t="n"/>
       <c r="I342" s="8" t="n"/>
@@ -12714,8 +12711,8 @@
         <f>IF(C343="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E343" s="16" t="n"/>
-      <c r="F343" s="16" t="n"/>
+      <c r="E343" s="9" t="n"/>
+      <c r="F343" s="9" t="n"/>
       <c r="G343" s="8" t="n"/>
       <c r="H343" s="8" t="n"/>
       <c r="I343" s="8" t="n"/>
@@ -12748,8 +12745,8 @@
         <f>IF(C344="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E344" s="16" t="n"/>
-      <c r="F344" s="16" t="n"/>
+      <c r="E344" s="9" t="n"/>
+      <c r="F344" s="9" t="n"/>
       <c r="G344" s="8" t="n"/>
       <c r="H344" s="8" t="n"/>
       <c r="I344" s="8" t="n"/>
@@ -12782,8 +12779,8 @@
         <f>IF(C345="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E345" s="16" t="n"/>
-      <c r="F345" s="16" t="n"/>
+      <c r="E345" s="9" t="n"/>
+      <c r="F345" s="9" t="n"/>
       <c r="G345" s="8" t="n"/>
       <c r="H345" s="8" t="n"/>
       <c r="I345" s="8" t="n"/>
@@ -12816,8 +12813,8 @@
         <f>IF(C346="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E346" s="16" t="n"/>
-      <c r="F346" s="16" t="n"/>
+      <c r="E346" s="9" t="n"/>
+      <c r="F346" s="9" t="n"/>
       <c r="G346" s="8" t="n"/>
       <c r="H346" s="8" t="n"/>
       <c r="I346" s="8" t="n"/>
@@ -12850,8 +12847,8 @@
         <f>IF(C347="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E347" s="16" t="n"/>
-      <c r="F347" s="16" t="n"/>
+      <c r="E347" s="9" t="n"/>
+      <c r="F347" s="9" t="n"/>
       <c r="G347" s="8" t="n"/>
       <c r="H347" s="8" t="n"/>
       <c r="I347" s="8" t="n"/>
@@ -12884,8 +12881,8 @@
         <f>IF(C348="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E348" s="16" t="n"/>
-      <c r="F348" s="16" t="n"/>
+      <c r="E348" s="9" t="n"/>
+      <c r="F348" s="9" t="n"/>
       <c r="G348" s="8" t="n"/>
       <c r="H348" s="8" t="n"/>
       <c r="I348" s="8" t="n"/>
@@ -12918,8 +12915,8 @@
         <f>IF(C349="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E349" s="16" t="n"/>
-      <c r="F349" s="16" t="n"/>
+      <c r="E349" s="9" t="n"/>
+      <c r="F349" s="9" t="n"/>
       <c r="G349" s="8" t="n"/>
       <c r="H349" s="8" t="n"/>
       <c r="I349" s="8" t="n"/>
@@ -12952,8 +12949,8 @@
         <f>IF(C350="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E350" s="16" t="n"/>
-      <c r="F350" s="16" t="n"/>
+      <c r="E350" s="9" t="n"/>
+      <c r="F350" s="9" t="n"/>
       <c r="G350" s="8" t="n"/>
       <c r="H350" s="8" t="n"/>
       <c r="I350" s="8" t="n"/>
@@ -12986,8 +12983,8 @@
         <f>IF(C351="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E351" s="16" t="n"/>
-      <c r="F351" s="16" t="n"/>
+      <c r="E351" s="9" t="n"/>
+      <c r="F351" s="9" t="n"/>
       <c r="G351" s="8" t="n"/>
       <c r="H351" s="8" t="n"/>
       <c r="I351" s="8" t="n"/>
@@ -13020,8 +13017,8 @@
         <f>IF(C352="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E352" s="16" t="n"/>
-      <c r="F352" s="16" t="n"/>
+      <c r="E352" s="9" t="n"/>
+      <c r="F352" s="9" t="n"/>
       <c r="G352" s="8" t="n"/>
       <c r="H352" s="8" t="n"/>
       <c r="I352" s="8" t="n"/>
@@ -13054,8 +13051,8 @@
         <f>IF(C353="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E353" s="16" t="n"/>
-      <c r="F353" s="16" t="n"/>
+      <c r="E353" s="9" t="n"/>
+      <c r="F353" s="9" t="n"/>
       <c r="G353" s="8" t="n"/>
       <c r="H353" s="8" t="n"/>
       <c r="I353" s="8" t="n"/>
@@ -13088,8 +13085,8 @@
         <f>IF(C354="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E354" s="16" t="n"/>
-      <c r="F354" s="16" t="n"/>
+      <c r="E354" s="9" t="n"/>
+      <c r="F354" s="9" t="n"/>
       <c r="G354" s="8" t="n"/>
       <c r="H354" s="8" t="n"/>
       <c r="I354" s="8" t="n"/>
@@ -13122,8 +13119,8 @@
         <f>IF(C355="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E355" s="16" t="n"/>
-      <c r="F355" s="16" t="n"/>
+      <c r="E355" s="9" t="n"/>
+      <c r="F355" s="9" t="n"/>
       <c r="G355" s="8" t="n"/>
       <c r="H355" s="8" t="n"/>
       <c r="I355" s="8" t="n"/>
@@ -13156,8 +13153,8 @@
         <f>IF(C356="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E356" s="16" t="n"/>
-      <c r="F356" s="16" t="n"/>
+      <c r="E356" s="9" t="n"/>
+      <c r="F356" s="9" t="n"/>
       <c r="G356" s="8" t="n"/>
       <c r="H356" s="8" t="n"/>
       <c r="I356" s="8" t="n"/>
@@ -13190,8 +13187,8 @@
         <f>IF(C357="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E357" s="16" t="n"/>
-      <c r="F357" s="16" t="n"/>
+      <c r="E357" s="9" t="n"/>
+      <c r="F357" s="9" t="n"/>
       <c r="G357" s="8" t="n"/>
       <c r="H357" s="8" t="n"/>
       <c r="I357" s="8" t="n"/>
@@ -13224,8 +13221,8 @@
         <f>IF(C358="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E358" s="16" t="n"/>
-      <c r="F358" s="16" t="n"/>
+      <c r="E358" s="9" t="n"/>
+      <c r="F358" s="9" t="n"/>
       <c r="G358" s="8" t="n"/>
       <c r="H358" s="8" t="n"/>
       <c r="I358" s="8" t="n"/>
@@ -13258,8 +13255,8 @@
         <f>IF(C359="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E359" s="16" t="n"/>
-      <c r="F359" s="16" t="n"/>
+      <c r="E359" s="9" t="n"/>
+      <c r="F359" s="9" t="n"/>
       <c r="G359" s="8" t="n"/>
       <c r="H359" s="8" t="n"/>
       <c r="I359" s="8" t="n"/>
@@ -13292,8 +13289,8 @@
         <f>IF(C360="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E360" s="16" t="n"/>
-      <c r="F360" s="16" t="n"/>
+      <c r="E360" s="9" t="n"/>
+      <c r="F360" s="9" t="n"/>
       <c r="G360" s="8" t="n"/>
       <c r="H360" s="8" t="n"/>
       <c r="I360" s="8" t="n"/>
@@ -13326,8 +13323,8 @@
         <f>IF(C361="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E361" s="16" t="n"/>
-      <c r="F361" s="16" t="n"/>
+      <c r="E361" s="9" t="n"/>
+      <c r="F361" s="9" t="n"/>
       <c r="G361" s="8" t="n"/>
       <c r="H361" s="8" t="n"/>
       <c r="I361" s="8" t="n"/>
@@ -13360,8 +13357,8 @@
         <f>IF(C362="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E362" s="16" t="n"/>
-      <c r="F362" s="16" t="n"/>
+      <c r="E362" s="9" t="n"/>
+      <c r="F362" s="9" t="n"/>
       <c r="G362" s="8" t="n"/>
       <c r="H362" s="8" t="n"/>
       <c r="I362" s="8" t="n"/>
@@ -13394,8 +13391,8 @@
         <f>IF(C363="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E363" s="16" t="n"/>
-      <c r="F363" s="16" t="n"/>
+      <c r="E363" s="9" t="n"/>
+      <c r="F363" s="9" t="n"/>
       <c r="G363" s="8" t="n"/>
       <c r="H363" s="8" t="n"/>
       <c r="I363" s="8" t="n"/>
@@ -13428,8 +13425,8 @@
         <f>IF(C364="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E364" s="16" t="n"/>
-      <c r="F364" s="16" t="n"/>
+      <c r="E364" s="9" t="n"/>
+      <c r="F364" s="9" t="n"/>
       <c r="G364" s="8" t="n"/>
       <c r="H364" s="8" t="n"/>
       <c r="I364" s="8" t="n"/>
@@ -13462,8 +13459,8 @@
         <f>IF(C365="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E365" s="16" t="n"/>
-      <c r="F365" s="16" t="n"/>
+      <c r="E365" s="9" t="n"/>
+      <c r="F365" s="9" t="n"/>
       <c r="G365" s="8" t="n"/>
       <c r="H365" s="8" t="n"/>
       <c r="I365" s="8" t="n"/>
@@ -13496,8 +13493,8 @@
         <f>IF(C366="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E366" s="16" t="n"/>
-      <c r="F366" s="16" t="n"/>
+      <c r="E366" s="9" t="n"/>
+      <c r="F366" s="9" t="n"/>
       <c r="G366" s="8" t="n"/>
       <c r="H366" s="8" t="n"/>
       <c r="I366" s="8" t="n"/>
@@ -13530,8 +13527,8 @@
         <f>IF(C367="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E367" s="16" t="n"/>
-      <c r="F367" s="16" t="n"/>
+      <c r="E367" s="9" t="n"/>
+      <c r="F367" s="9" t="n"/>
       <c r="G367" s="8" t="n"/>
       <c r="H367" s="8" t="n"/>
       <c r="I367" s="8" t="n"/>
@@ -13564,8 +13561,8 @@
         <f>IF(C368="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E368" s="16" t="n"/>
-      <c r="F368" s="16" t="n"/>
+      <c r="E368" s="9" t="n"/>
+      <c r="F368" s="9" t="n"/>
       <c r="G368" s="8" t="n"/>
       <c r="H368" s="8" t="n"/>
       <c r="I368" s="8" t="n"/>
@@ -13598,8 +13595,8 @@
         <f>IF(C369="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E369" s="16" t="n"/>
-      <c r="F369" s="16" t="n"/>
+      <c r="E369" s="9" t="n"/>
+      <c r="F369" s="9" t="n"/>
       <c r="G369" s="8" t="n"/>
       <c r="H369" s="8" t="n"/>
       <c r="I369" s="8" t="n"/>
@@ -13632,8 +13629,8 @@
         <f>IF(C370="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E370" s="16" t="n"/>
-      <c r="F370" s="16" t="n"/>
+      <c r="E370" s="9" t="n"/>
+      <c r="F370" s="9" t="n"/>
       <c r="G370" s="8" t="n"/>
       <c r="H370" s="8" t="n"/>
       <c r="I370" s="8" t="n"/>
@@ -13666,8 +13663,8 @@
         <f>IF(C371="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E371" s="16" t="n"/>
-      <c r="F371" s="16" t="n"/>
+      <c r="E371" s="9" t="n"/>
+      <c r="F371" s="9" t="n"/>
       <c r="G371" s="8" t="n"/>
       <c r="H371" s="8" t="n"/>
       <c r="I371" s="8" t="n"/>
@@ -13700,8 +13697,8 @@
         <f>IF(C372="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E372" s="16" t="n"/>
-      <c r="F372" s="16" t="n"/>
+      <c r="E372" s="9" t="n"/>
+      <c r="F372" s="9" t="n"/>
       <c r="G372" s="8" t="n"/>
       <c r="H372" s="8" t="n"/>
       <c r="I372" s="8" t="n"/>
@@ -13734,8 +13731,8 @@
         <f>IF(C373="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E373" s="16" t="n"/>
-      <c r="F373" s="16" t="n"/>
+      <c r="E373" s="9" t="n"/>
+      <c r="F373" s="9" t="n"/>
       <c r="G373" s="8" t="n"/>
       <c r="H373" s="8" t="n"/>
       <c r="I373" s="8" t="n"/>
@@ -13768,8 +13765,8 @@
         <f>IF(C374="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E374" s="16" t="n"/>
-      <c r="F374" s="16" t="n"/>
+      <c r="E374" s="9" t="n"/>
+      <c r="F374" s="9" t="n"/>
       <c r="G374" s="8" t="n"/>
       <c r="H374" s="8" t="n"/>
       <c r="I374" s="8" t="n"/>
@@ -13802,8 +13799,8 @@
         <f>IF(C375="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E375" s="16" t="n"/>
-      <c r="F375" s="16" t="n"/>
+      <c r="E375" s="9" t="n"/>
+      <c r="F375" s="9" t="n"/>
       <c r="G375" s="8" t="n"/>
       <c r="H375" s="8" t="n"/>
       <c r="I375" s="8" t="n"/>
@@ -13836,8 +13833,8 @@
         <f>IF(C376="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E376" s="16" t="n"/>
-      <c r="F376" s="16" t="n"/>
+      <c r="E376" s="9" t="n"/>
+      <c r="F376" s="9" t="n"/>
       <c r="G376" s="8" t="n"/>
       <c r="H376" s="8" t="n"/>
       <c r="I376" s="8" t="n"/>
@@ -13870,8 +13867,8 @@
         <f>IF(C377="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E377" s="16" t="n"/>
-      <c r="F377" s="16" t="n"/>
+      <c r="E377" s="9" t="n"/>
+      <c r="F377" s="9" t="n"/>
       <c r="G377" s="8" t="n"/>
       <c r="H377" s="8" t="n"/>
       <c r="I377" s="8" t="n"/>
@@ -13904,8 +13901,8 @@
         <f>IF(C378="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E378" s="16" t="n"/>
-      <c r="F378" s="16" t="n"/>
+      <c r="E378" s="9" t="n"/>
+      <c r="F378" s="9" t="n"/>
       <c r="G378" s="8" t="n"/>
       <c r="H378" s="8" t="n"/>
       <c r="I378" s="8" t="n"/>
@@ -13938,8 +13935,8 @@
         <f>IF(C379="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E379" s="16" t="n"/>
-      <c r="F379" s="16" t="n"/>
+      <c r="E379" s="9" t="n"/>
+      <c r="F379" s="9" t="n"/>
       <c r="G379" s="8" t="n"/>
       <c r="H379" s="8" t="n"/>
       <c r="I379" s="8" t="n"/>
@@ -13972,8 +13969,8 @@
         <f>IF(C380="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E380" s="16" t="n"/>
-      <c r="F380" s="16" t="n"/>
+      <c r="E380" s="9" t="n"/>
+      <c r="F380" s="9" t="n"/>
       <c r="G380" s="8" t="n"/>
       <c r="H380" s="8" t="n"/>
       <c r="I380" s="8" t="n"/>
@@ -14006,8 +14003,8 @@
         <f>IF(C381="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E381" s="16" t="n"/>
-      <c r="F381" s="16" t="n"/>
+      <c r="E381" s="9" t="n"/>
+      <c r="F381" s="9" t="n"/>
       <c r="G381" s="8" t="n"/>
       <c r="H381" s="8" t="n"/>
       <c r="I381" s="8" t="n"/>
@@ -14040,8 +14037,8 @@
         <f>IF(C382="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E382" s="16" t="n"/>
-      <c r="F382" s="16" t="n"/>
+      <c r="E382" s="9" t="n"/>
+      <c r="F382" s="9" t="n"/>
       <c r="G382" s="8" t="n"/>
       <c r="H382" s="8" t="n"/>
       <c r="I382" s="8" t="n"/>
@@ -14074,8 +14071,8 @@
         <f>IF(C383="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E383" s="16" t="n"/>
-      <c r="F383" s="16" t="n"/>
+      <c r="E383" s="9" t="n"/>
+      <c r="F383" s="9" t="n"/>
       <c r="G383" s="8" t="n"/>
       <c r="H383" s="8" t="n"/>
       <c r="I383" s="8" t="n"/>
@@ -14108,8 +14105,8 @@
         <f>IF(C384="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E384" s="16" t="n"/>
-      <c r="F384" s="16" t="n"/>
+      <c r="E384" s="9" t="n"/>
+      <c r="F384" s="9" t="n"/>
       <c r="G384" s="8" t="n"/>
       <c r="H384" s="8" t="n"/>
       <c r="I384" s="8" t="n"/>
@@ -14142,8 +14139,8 @@
         <f>IF(C385="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E385" s="16" t="n"/>
-      <c r="F385" s="16" t="n"/>
+      <c r="E385" s="9" t="n"/>
+      <c r="F385" s="9" t="n"/>
       <c r="G385" s="8" t="n"/>
       <c r="H385" s="8" t="n"/>
       <c r="I385" s="8" t="n"/>
@@ -14176,8 +14173,8 @@
         <f>IF(C386="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E386" s="16" t="n"/>
-      <c r="F386" s="16" t="n"/>
+      <c r="E386" s="9" t="n"/>
+      <c r="F386" s="9" t="n"/>
       <c r="G386" s="8" t="n"/>
       <c r="H386" s="8" t="n"/>
       <c r="I386" s="8" t="n"/>
@@ -14210,8 +14207,8 @@
         <f>IF(C387="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E387" s="16" t="n"/>
-      <c r="F387" s="16" t="n"/>
+      <c r="E387" s="9" t="n"/>
+      <c r="F387" s="9" t="n"/>
       <c r="G387" s="8" t="n"/>
       <c r="H387" s="8" t="n"/>
       <c r="I387" s="8" t="n"/>
@@ -14244,8 +14241,8 @@
         <f>IF(C388="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E388" s="16" t="n"/>
-      <c r="F388" s="16" t="n"/>
+      <c r="E388" s="9" t="n"/>
+      <c r="F388" s="9" t="n"/>
       <c r="G388" s="8" t="n"/>
       <c r="H388" s="8" t="n"/>
       <c r="I388" s="8" t="n"/>
@@ -14278,8 +14275,8 @@
         <f>IF(C389="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E389" s="16" t="n"/>
-      <c r="F389" s="16" t="n"/>
+      <c r="E389" s="9" t="n"/>
+      <c r="F389" s="9" t="n"/>
       <c r="G389" s="8" t="n"/>
       <c r="H389" s="8" t="n"/>
       <c r="I389" s="8" t="n"/>
@@ -14312,8 +14309,8 @@
         <f>IF(C390="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E390" s="16" t="n"/>
-      <c r="F390" s="16" t="n"/>
+      <c r="E390" s="9" t="n"/>
+      <c r="F390" s="9" t="n"/>
       <c r="G390" s="8" t="n"/>
       <c r="H390" s="8" t="n"/>
       <c r="I390" s="8" t="n"/>
@@ -14346,8 +14343,8 @@
         <f>IF(C391="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E391" s="16" t="n"/>
-      <c r="F391" s="16" t="n"/>
+      <c r="E391" s="9" t="n"/>
+      <c r="F391" s="9" t="n"/>
       <c r="G391" s="8" t="n"/>
       <c r="H391" s="8" t="n"/>
       <c r="I391" s="8" t="n"/>
@@ -14380,8 +14377,8 @@
         <f>IF(C392="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E392" s="16" t="n"/>
-      <c r="F392" s="16" t="n"/>
+      <c r="E392" s="9" t="n"/>
+      <c r="F392" s="9" t="n"/>
       <c r="G392" s="8" t="n"/>
       <c r="H392" s="8" t="n"/>
       <c r="I392" s="8" t="n"/>
@@ -14414,8 +14411,8 @@
         <f>IF(C393="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E393" s="16" t="n"/>
-      <c r="F393" s="16" t="n"/>
+      <c r="E393" s="9" t="n"/>
+      <c r="F393" s="9" t="n"/>
       <c r="G393" s="8" t="n"/>
       <c r="H393" s="8" t="n"/>
       <c r="I393" s="8" t="n"/>
@@ -14448,8 +14445,8 @@
         <f>IF(C394="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E394" s="16" t="n"/>
-      <c r="F394" s="16" t="n"/>
+      <c r="E394" s="9" t="n"/>
+      <c r="F394" s="9" t="n"/>
       <c r="G394" s="8" t="n"/>
       <c r="H394" s="8" t="n"/>
       <c r="I394" s="8" t="n"/>
@@ -14482,8 +14479,8 @@
         <f>IF(C395="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E395" s="16" t="n"/>
-      <c r="F395" s="16" t="n"/>
+      <c r="E395" s="9" t="n"/>
+      <c r="F395" s="9" t="n"/>
       <c r="G395" s="8" t="n"/>
       <c r="H395" s="8" t="n"/>
       <c r="I395" s="8" t="n"/>
@@ -14516,8 +14513,8 @@
         <f>IF(C396="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E396" s="16" t="n"/>
-      <c r="F396" s="16" t="n"/>
+      <c r="E396" s="9" t="n"/>
+      <c r="F396" s="9" t="n"/>
       <c r="G396" s="8" t="n"/>
       <c r="H396" s="8" t="n"/>
       <c r="I396" s="8" t="n"/>
@@ -14550,8 +14547,8 @@
         <f>IF(C397="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E397" s="16" t="n"/>
-      <c r="F397" s="16" t="n"/>
+      <c r="E397" s="9" t="n"/>
+      <c r="F397" s="9" t="n"/>
       <c r="G397" s="8" t="n"/>
       <c r="H397" s="8" t="n"/>
       <c r="I397" s="8" t="n"/>
@@ -14584,8 +14581,8 @@
         <f>IF(C398="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E398" s="16" t="n"/>
-      <c r="F398" s="16" t="n"/>
+      <c r="E398" s="9" t="n"/>
+      <c r="F398" s="9" t="n"/>
       <c r="G398" s="8" t="n"/>
       <c r="H398" s="8" t="n"/>
       <c r="I398" s="8" t="n"/>
@@ -14618,8 +14615,8 @@
         <f>IF(C399="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E399" s="16" t="n"/>
-      <c r="F399" s="16" t="n"/>
+      <c r="E399" s="9" t="n"/>
+      <c r="F399" s="9" t="n"/>
       <c r="G399" s="8" t="n"/>
       <c r="H399" s="8" t="n"/>
       <c r="I399" s="8" t="n"/>
@@ -14652,8 +14649,8 @@
         <f>IF(C400="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E400" s="16" t="n"/>
-      <c r="F400" s="16" t="n"/>
+      <c r="E400" s="9" t="n"/>
+      <c r="F400" s="9" t="n"/>
       <c r="G400" s="8" t="n"/>
       <c r="H400" s="8" t="n"/>
       <c r="I400" s="8" t="n"/>
@@ -14686,8 +14683,8 @@
         <f>IF(C401="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E401" s="16" t="n"/>
-      <c r="F401" s="16" t="n"/>
+      <c r="E401" s="9" t="n"/>
+      <c r="F401" s="9" t="n"/>
       <c r="G401" s="8" t="n"/>
       <c r="H401" s="8" t="n"/>
       <c r="I401" s="8" t="n"/>
@@ -14720,8 +14717,8 @@
         <f>IF(C402="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E402" s="16" t="n"/>
-      <c r="F402" s="16" t="n"/>
+      <c r="E402" s="9" t="n"/>
+      <c r="F402" s="9" t="n"/>
       <c r="G402" s="8" t="n"/>
       <c r="H402" s="8" t="n"/>
       <c r="I402" s="8" t="n"/>
@@ -14754,8 +14751,8 @@
         <f>IF(C403="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E403" s="16" t="n"/>
-      <c r="F403" s="16" t="n"/>
+      <c r="E403" s="9" t="n"/>
+      <c r="F403" s="9" t="n"/>
       <c r="G403" s="8" t="n"/>
       <c r="H403" s="8" t="n"/>
       <c r="I403" s="8" t="n"/>
@@ -14788,8 +14785,8 @@
         <f>IF(C404="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E404" s="16" t="n"/>
-      <c r="F404" s="16" t="n"/>
+      <c r="E404" s="9" t="n"/>
+      <c r="F404" s="9" t="n"/>
       <c r="G404" s="8" t="n"/>
       <c r="H404" s="8" t="n"/>
       <c r="I404" s="8" t="n"/>
@@ -14822,8 +14819,8 @@
         <f>IF(C405="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E405" s="16" t="n"/>
-      <c r="F405" s="16" t="n"/>
+      <c r="E405" s="9" t="n"/>
+      <c r="F405" s="9" t="n"/>
       <c r="G405" s="8" t="n"/>
       <c r="H405" s="8" t="n"/>
       <c r="I405" s="8" t="n"/>
@@ -14856,8 +14853,8 @@
         <f>IF(C406="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E406" s="16" t="n"/>
-      <c r="F406" s="16" t="n"/>
+      <c r="E406" s="9" t="n"/>
+      <c r="F406" s="9" t="n"/>
       <c r="G406" s="8" t="n"/>
       <c r="H406" s="8" t="n"/>
       <c r="I406" s="8" t="n"/>
@@ -14890,8 +14887,8 @@
         <f>IF(C407="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E407" s="16" t="n"/>
-      <c r="F407" s="16" t="n"/>
+      <c r="E407" s="9" t="n"/>
+      <c r="F407" s="9" t="n"/>
       <c r="G407" s="8" t="n"/>
       <c r="H407" s="8" t="n"/>
       <c r="I407" s="8" t="n"/>
@@ -14924,8 +14921,8 @@
         <f>IF(C408="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E408" s="16" t="n"/>
-      <c r="F408" s="16" t="n"/>
+      <c r="E408" s="9" t="n"/>
+      <c r="F408" s="9" t="n"/>
       <c r="G408" s="8" t="n"/>
       <c r="H408" s="8" t="n"/>
       <c r="I408" s="8" t="n"/>
@@ -14958,8 +14955,8 @@
         <f>IF(C409="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E409" s="16" t="n"/>
-      <c r="F409" s="16" t="n"/>
+      <c r="E409" s="9" t="n"/>
+      <c r="F409" s="9" t="n"/>
       <c r="G409" s="8" t="n"/>
       <c r="H409" s="8" t="n"/>
       <c r="I409" s="8" t="n"/>
@@ -14992,8 +14989,8 @@
         <f>IF(C410="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E410" s="16" t="n"/>
-      <c r="F410" s="16" t="n"/>
+      <c r="E410" s="9" t="n"/>
+      <c r="F410" s="9" t="n"/>
       <c r="G410" s="8" t="n"/>
       <c r="H410" s="8" t="n"/>
       <c r="I410" s="8" t="n"/>
@@ -15026,8 +15023,8 @@
         <f>IF(C411="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E411" s="16" t="n"/>
-      <c r="F411" s="16" t="n"/>
+      <c r="E411" s="9" t="n"/>
+      <c r="F411" s="9" t="n"/>
       <c r="G411" s="8" t="n"/>
       <c r="H411" s="8" t="n"/>
       <c r="I411" s="8" t="n"/>
@@ -15060,8 +15057,8 @@
         <f>IF(C412="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E412" s="16" t="n"/>
-      <c r="F412" s="16" t="n"/>
+      <c r="E412" s="9" t="n"/>
+      <c r="F412" s="9" t="n"/>
       <c r="G412" s="8" t="n"/>
       <c r="H412" s="8" t="n"/>
       <c r="I412" s="8" t="n"/>
@@ -15094,8 +15091,8 @@
         <f>IF(C413="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E413" s="16" t="n"/>
-      <c r="F413" s="16" t="n"/>
+      <c r="E413" s="9" t="n"/>
+      <c r="F413" s="9" t="n"/>
       <c r="G413" s="8" t="n"/>
       <c r="H413" s="8" t="n"/>
       <c r="I413" s="8" t="n"/>
@@ -15128,8 +15125,8 @@
         <f>IF(C414="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E414" s="16" t="n"/>
-      <c r="F414" s="16" t="n"/>
+      <c r="E414" s="9" t="n"/>
+      <c r="F414" s="9" t="n"/>
       <c r="G414" s="8" t="n"/>
       <c r="H414" s="8" t="n"/>
       <c r="I414" s="8" t="n"/>
@@ -15162,8 +15159,8 @@
         <f>IF(C415="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E415" s="16" t="n"/>
-      <c r="F415" s="16" t="n"/>
+      <c r="E415" s="9" t="n"/>
+      <c r="F415" s="9" t="n"/>
       <c r="G415" s="8" t="n"/>
       <c r="H415" s="8" t="n"/>
       <c r="I415" s="8" t="n"/>
@@ -15196,8 +15193,8 @@
         <f>IF(C416="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E416" s="16" t="n"/>
-      <c r="F416" s="16" t="n"/>
+      <c r="E416" s="9" t="n"/>
+      <c r="F416" s="9" t="n"/>
       <c r="G416" s="8" t="n"/>
       <c r="H416" s="8" t="n"/>
       <c r="I416" s="8" t="n"/>
@@ -15230,8 +15227,8 @@
         <f>IF(C417="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E417" s="16" t="n"/>
-      <c r="F417" s="16" t="n"/>
+      <c r="E417" s="9" t="n"/>
+      <c r="F417" s="9" t="n"/>
       <c r="G417" s="8" t="n"/>
       <c r="H417" s="8" t="n"/>
       <c r="I417" s="8" t="n"/>
@@ -15264,8 +15261,8 @@
         <f>IF(C418="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E418" s="16" t="n"/>
-      <c r="F418" s="16" t="n"/>
+      <c r="E418" s="9" t="n"/>
+      <c r="F418" s="9" t="n"/>
       <c r="G418" s="8" t="n"/>
       <c r="H418" s="8" t="n"/>
       <c r="I418" s="8" t="n"/>
@@ -15298,8 +15295,8 @@
         <f>IF(C419="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E419" s="16" t="n"/>
-      <c r="F419" s="16" t="n"/>
+      <c r="E419" s="9" t="n"/>
+      <c r="F419" s="9" t="n"/>
       <c r="G419" s="8" t="n"/>
       <c r="H419" s="8" t="n"/>
       <c r="I419" s="8" t="n"/>
@@ -15332,8 +15329,8 @@
         <f>IF(C420="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E420" s="16" t="n"/>
-      <c r="F420" s="16" t="n"/>
+      <c r="E420" s="9" t="n"/>
+      <c r="F420" s="9" t="n"/>
       <c r="G420" s="8" t="n"/>
       <c r="H420" s="8" t="n"/>
       <c r="I420" s="8" t="n"/>
@@ -15366,8 +15363,8 @@
         <f>IF(C421="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E421" s="16" t="n"/>
-      <c r="F421" s="16" t="n"/>
+      <c r="E421" s="9" t="n"/>
+      <c r="F421" s="9" t="n"/>
       <c r="G421" s="8" t="n"/>
       <c r="H421" s="8" t="n"/>
       <c r="I421" s="8" t="n"/>
@@ -15400,8 +15397,8 @@
         <f>IF(C422="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E422" s="16" t="n"/>
-      <c r="F422" s="16" t="n"/>
+      <c r="E422" s="9" t="n"/>
+      <c r="F422" s="9" t="n"/>
       <c r="G422" s="8" t="n"/>
       <c r="H422" s="8" t="n"/>
       <c r="I422" s="8" t="n"/>
@@ -15434,8 +15431,8 @@
         <f>IF(C423="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E423" s="16" t="n"/>
-      <c r="F423" s="16" t="n"/>
+      <c r="E423" s="9" t="n"/>
+      <c r="F423" s="9" t="n"/>
       <c r="G423" s="8" t="n"/>
       <c r="H423" s="8" t="n"/>
       <c r="I423" s="8" t="n"/>
@@ -15468,8 +15465,8 @@
         <f>IF(C424="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E424" s="16" t="n"/>
-      <c r="F424" s="16" t="n"/>
+      <c r="E424" s="9" t="n"/>
+      <c r="F424" s="9" t="n"/>
       <c r="G424" s="8" t="n"/>
       <c r="H424" s="8" t="n"/>
       <c r="I424" s="8" t="n"/>
@@ -15502,8 +15499,8 @@
         <f>IF(C425="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E425" s="16" t="n"/>
-      <c r="F425" s="16" t="n"/>
+      <c r="E425" s="9" t="n"/>
+      <c r="F425" s="9" t="n"/>
       <c r="G425" s="8" t="n"/>
       <c r="H425" s="8" t="n"/>
       <c r="I425" s="8" t="n"/>
@@ -15536,8 +15533,8 @@
         <f>IF(C426="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E426" s="16" t="n"/>
-      <c r="F426" s="16" t="n"/>
+      <c r="E426" s="9" t="n"/>
+      <c r="F426" s="9" t="n"/>
       <c r="G426" s="8" t="n"/>
       <c r="H426" s="8" t="n"/>
       <c r="I426" s="8" t="n"/>
@@ -15570,8 +15567,8 @@
         <f>IF(C427="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E427" s="16" t="n"/>
-      <c r="F427" s="16" t="n"/>
+      <c r="E427" s="9" t="n"/>
+      <c r="F427" s="9" t="n"/>
       <c r="G427" s="8" t="n"/>
       <c r="H427" s="8" t="n"/>
       <c r="I427" s="8" t="n"/>
@@ -15604,8 +15601,8 @@
         <f>IF(C428="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E428" s="16" t="n"/>
-      <c r="F428" s="16" t="n"/>
+      <c r="E428" s="9" t="n"/>
+      <c r="F428" s="9" t="n"/>
       <c r="G428" s="8" t="n"/>
       <c r="H428" s="8" t="n"/>
       <c r="I428" s="8" t="n"/>
@@ -15638,8 +15635,8 @@
         <f>IF(C429="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E429" s="16" t="n"/>
-      <c r="F429" s="16" t="n"/>
+      <c r="E429" s="9" t="n"/>
+      <c r="F429" s="9" t="n"/>
       <c r="G429" s="8" t="n"/>
       <c r="H429" s="8" t="n"/>
       <c r="I429" s="8" t="n"/>
@@ -15672,8 +15669,8 @@
         <f>IF(C430="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E430" s="16" t="n"/>
-      <c r="F430" s="16" t="n"/>
+      <c r="E430" s="9" t="n"/>
+      <c r="F430" s="9" t="n"/>
       <c r="G430" s="8" t="n"/>
       <c r="H430" s="8" t="n"/>
       <c r="I430" s="8" t="n"/>
@@ -15706,8 +15703,8 @@
         <f>IF(C431="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E431" s="16" t="n"/>
-      <c r="F431" s="16" t="n"/>
+      <c r="E431" s="9" t="n"/>
+      <c r="F431" s="9" t="n"/>
       <c r="G431" s="8" t="n"/>
       <c r="H431" s="8" t="n"/>
       <c r="I431" s="8" t="n"/>
@@ -15740,8 +15737,8 @@
         <f>IF(C432="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E432" s="16" t="n"/>
-      <c r="F432" s="16" t="n"/>
+      <c r="E432" s="9" t="n"/>
+      <c r="F432" s="9" t="n"/>
       <c r="G432" s="8" t="n"/>
       <c r="H432" s="8" t="n"/>
       <c r="I432" s="8" t="n"/>
@@ -15774,8 +15771,8 @@
         <f>IF(C433="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E433" s="16" t="n"/>
-      <c r="F433" s="16" t="n"/>
+      <c r="E433" s="9" t="n"/>
+      <c r="F433" s="9" t="n"/>
       <c r="G433" s="8" t="n"/>
       <c r="H433" s="8" t="n"/>
       <c r="I433" s="8" t="n"/>
@@ -15808,8 +15805,8 @@
         <f>IF(C434="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E434" s="16" t="n"/>
-      <c r="F434" s="16" t="n"/>
+      <c r="E434" s="9" t="n"/>
+      <c r="F434" s="9" t="n"/>
       <c r="G434" s="8" t="n"/>
       <c r="H434" s="8" t="n"/>
       <c r="I434" s="8" t="n"/>
@@ -15842,8 +15839,8 @@
         <f>IF(C435="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E435" s="16" t="n"/>
-      <c r="F435" s="16" t="n"/>
+      <c r="E435" s="9" t="n"/>
+      <c r="F435" s="9" t="n"/>
       <c r="G435" s="8" t="n"/>
       <c r="H435" s="8" t="n"/>
       <c r="I435" s="8" t="n"/>
@@ -15876,8 +15873,8 @@
         <f>IF(C436="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E436" s="16" t="n"/>
-      <c r="F436" s="16" t="n"/>
+      <c r="E436" s="9" t="n"/>
+      <c r="F436" s="9" t="n"/>
       <c r="G436" s="8" t="n"/>
       <c r="H436" s="8" t="n"/>
       <c r="I436" s="8" t="n"/>
@@ -15910,8 +15907,8 @@
         <f>IF(C437="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E437" s="16" t="n"/>
-      <c r="F437" s="16" t="n"/>
+      <c r="E437" s="9" t="n"/>
+      <c r="F437" s="9" t="n"/>
       <c r="G437" s="8" t="n"/>
       <c r="H437" s="8" t="n"/>
       <c r="I437" s="8" t="n"/>
@@ -15944,8 +15941,8 @@
         <f>IF(C438="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E438" s="16" t="n"/>
-      <c r="F438" s="16" t="n"/>
+      <c r="E438" s="9" t="n"/>
+      <c r="F438" s="9" t="n"/>
       <c r="G438" s="8" t="n"/>
       <c r="H438" s="8" t="n"/>
       <c r="I438" s="8" t="n"/>
@@ -15978,8 +15975,8 @@
         <f>IF(C439="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E439" s="16" t="n"/>
-      <c r="F439" s="16" t="n"/>
+      <c r="E439" s="9" t="n"/>
+      <c r="F439" s="9" t="n"/>
       <c r="G439" s="8" t="n"/>
       <c r="H439" s="8" t="n"/>
       <c r="I439" s="8" t="n"/>
@@ -16012,8 +16009,8 @@
         <f>IF(C440="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E440" s="16" t="n"/>
-      <c r="F440" s="16" t="n"/>
+      <c r="E440" s="9" t="n"/>
+      <c r="F440" s="9" t="n"/>
       <c r="G440" s="8" t="n"/>
       <c r="H440" s="8" t="n"/>
       <c r="I440" s="8" t="n"/>
@@ -16046,8 +16043,8 @@
         <f>IF(C441="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E441" s="16" t="n"/>
-      <c r="F441" s="16" t="n"/>
+      <c r="E441" s="9" t="n"/>
+      <c r="F441" s="9" t="n"/>
       <c r="G441" s="8" t="n"/>
       <c r="H441" s="8" t="n"/>
       <c r="I441" s="8" t="n"/>
@@ -16080,8 +16077,8 @@
         <f>IF(C442="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E442" s="16" t="n"/>
-      <c r="F442" s="16" t="n"/>
+      <c r="E442" s="9" t="n"/>
+      <c r="F442" s="9" t="n"/>
       <c r="G442" s="8" t="n"/>
       <c r="H442" s="8" t="n"/>
       <c r="I442" s="8" t="n"/>
@@ -16114,8 +16111,8 @@
         <f>IF(C443="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E443" s="16" t="n"/>
-      <c r="F443" s="16" t="n"/>
+      <c r="E443" s="9" t="n"/>
+      <c r="F443" s="9" t="n"/>
       <c r="G443" s="8" t="n"/>
       <c r="H443" s="8" t="n"/>
       <c r="I443" s="8" t="n"/>
@@ -16148,8 +16145,8 @@
         <f>IF(C444="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E444" s="16" t="n"/>
-      <c r="F444" s="16" t="n"/>
+      <c r="E444" s="9" t="n"/>
+      <c r="F444" s="9" t="n"/>
       <c r="G444" s="8" t="n"/>
       <c r="H444" s="8" t="n"/>
       <c r="I444" s="8" t="n"/>
@@ -16182,8 +16179,8 @@
         <f>IF(C445="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E445" s="16" t="n"/>
-      <c r="F445" s="16" t="n"/>
+      <c r="E445" s="9" t="n"/>
+      <c r="F445" s="9" t="n"/>
       <c r="G445" s="8" t="n"/>
       <c r="H445" s="8" t="n"/>
       <c r="I445" s="8" t="n"/>
@@ -16216,8 +16213,8 @@
         <f>IF(C446="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E446" s="16" t="n"/>
-      <c r="F446" s="16" t="n"/>
+      <c r="E446" s="9" t="n"/>
+      <c r="F446" s="9" t="n"/>
       <c r="G446" s="8" t="n"/>
       <c r="H446" s="8" t="n"/>
       <c r="I446" s="8" t="n"/>
@@ -16250,8 +16247,8 @@
         <f>IF(C447="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E447" s="16" t="n"/>
-      <c r="F447" s="16" t="n"/>
+      <c r="E447" s="9" t="n"/>
+      <c r="F447" s="9" t="n"/>
       <c r="G447" s="8" t="n"/>
       <c r="H447" s="8" t="n"/>
       <c r="I447" s="8" t="n"/>
@@ -16284,8 +16281,8 @@
         <f>IF(C448="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E448" s="16" t="n"/>
-      <c r="F448" s="16" t="n"/>
+      <c r="E448" s="9" t="n"/>
+      <c r="F448" s="9" t="n"/>
       <c r="G448" s="8" t="n"/>
       <c r="H448" s="8" t="n"/>
       <c r="I448" s="8" t="n"/>
@@ -16318,8 +16315,8 @@
         <f>IF(C449="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E449" s="16" t="n"/>
-      <c r="F449" s="16" t="n"/>
+      <c r="E449" s="9" t="n"/>
+      <c r="F449" s="9" t="n"/>
       <c r="G449" s="8" t="n"/>
       <c r="H449" s="8" t="n"/>
       <c r="I449" s="8" t="n"/>
@@ -16352,8 +16349,8 @@
         <f>IF(C450="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E450" s="16" t="n"/>
-      <c r="F450" s="16" t="n"/>
+      <c r="E450" s="9" t="n"/>
+      <c r="F450" s="9" t="n"/>
       <c r="G450" s="8" t="n"/>
       <c r="H450" s="8" t="n"/>
       <c r="I450" s="8" t="n"/>
@@ -16386,8 +16383,8 @@
         <f>IF(C451="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E451" s="16" t="n"/>
-      <c r="F451" s="16" t="n"/>
+      <c r="E451" s="9" t="n"/>
+      <c r="F451" s="9" t="n"/>
       <c r="G451" s="8" t="n"/>
       <c r="H451" s="8" t="n"/>
       <c r="I451" s="8" t="n"/>
@@ -16420,8 +16417,8 @@
         <f>IF(C452="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E452" s="16" t="n"/>
-      <c r="F452" s="16" t="n"/>
+      <c r="E452" s="9" t="n"/>
+      <c r="F452" s="9" t="n"/>
       <c r="G452" s="8" t="n"/>
       <c r="H452" s="8" t="n"/>
       <c r="I452" s="8" t="n"/>
@@ -16454,8 +16451,8 @@
         <f>IF(C453="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E453" s="16" t="n"/>
-      <c r="F453" s="16" t="n"/>
+      <c r="E453" s="9" t="n"/>
+      <c r="F453" s="9" t="n"/>
       <c r="G453" s="8" t="n"/>
       <c r="H453" s="8" t="n"/>
       <c r="I453" s="8" t="n"/>
@@ -16488,8 +16485,8 @@
         <f>IF(C454="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E454" s="16" t="n"/>
-      <c r="F454" s="16" t="n"/>
+      <c r="E454" s="9" t="n"/>
+      <c r="F454" s="9" t="n"/>
       <c r="G454" s="8" t="n"/>
       <c r="H454" s="8" t="n"/>
       <c r="I454" s="8" t="n"/>
@@ -16522,8 +16519,8 @@
         <f>IF(C455="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E455" s="16" t="n"/>
-      <c r="F455" s="16" t="n"/>
+      <c r="E455" s="9" t="n"/>
+      <c r="F455" s="9" t="n"/>
       <c r="G455" s="8" t="n"/>
       <c r="H455" s="8" t="n"/>
       <c r="I455" s="8" t="n"/>
@@ -16556,8 +16553,8 @@
         <f>IF(C456="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E456" s="16" t="n"/>
-      <c r="F456" s="16" t="n"/>
+      <c r="E456" s="9" t="n"/>
+      <c r="F456" s="9" t="n"/>
       <c r="G456" s="8" t="n"/>
       <c r="H456" s="8" t="n"/>
       <c r="I456" s="8" t="n"/>
@@ -16590,8 +16587,8 @@
         <f>IF(C457="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E457" s="16" t="n"/>
-      <c r="F457" s="16" t="n"/>
+      <c r="E457" s="9" t="n"/>
+      <c r="F457" s="9" t="n"/>
       <c r="G457" s="8" t="n"/>
       <c r="H457" s="8" t="n"/>
       <c r="I457" s="8" t="n"/>
@@ -16624,8 +16621,8 @@
         <f>IF(C458="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E458" s="16" t="n"/>
-      <c r="F458" s="16" t="n"/>
+      <c r="E458" s="9" t="n"/>
+      <c r="F458" s="9" t="n"/>
       <c r="G458" s="8" t="n"/>
       <c r="H458" s="8" t="n"/>
       <c r="I458" s="8" t="n"/>
@@ -16658,8 +16655,8 @@
         <f>IF(C459="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E459" s="16" t="n"/>
-      <c r="F459" s="16" t="n"/>
+      <c r="E459" s="9" t="n"/>
+      <c r="F459" s="9" t="n"/>
       <c r="G459" s="8" t="n"/>
       <c r="H459" s="8" t="n"/>
       <c r="I459" s="8" t="n"/>
@@ -16692,8 +16689,8 @@
         <f>IF(C460="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E460" s="16" t="n"/>
-      <c r="F460" s="16" t="n"/>
+      <c r="E460" s="9" t="n"/>
+      <c r="F460" s="9" t="n"/>
       <c r="G460" s="8" t="n"/>
       <c r="H460" s="8" t="n"/>
       <c r="I460" s="8" t="n"/>
@@ -16726,8 +16723,8 @@
         <f>IF(C461="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E461" s="16" t="n"/>
-      <c r="F461" s="16" t="n"/>
+      <c r="E461" s="9" t="n"/>
+      <c r="F461" s="9" t="n"/>
       <c r="G461" s="8" t="n"/>
       <c r="H461" s="8" t="n"/>
       <c r="I461" s="8" t="n"/>
@@ -16760,8 +16757,8 @@
         <f>IF(C462="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E462" s="16" t="n"/>
-      <c r="F462" s="16" t="n"/>
+      <c r="E462" s="9" t="n"/>
+      <c r="F462" s="9" t="n"/>
       <c r="G462" s="8" t="n"/>
       <c r="H462" s="8" t="n"/>
       <c r="I462" s="8" t="n"/>
@@ -16794,8 +16791,8 @@
         <f>IF(C463="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E463" s="16" t="n"/>
-      <c r="F463" s="16" t="n"/>
+      <c r="E463" s="9" t="n"/>
+      <c r="F463" s="9" t="n"/>
       <c r="G463" s="8" t="n"/>
       <c r="H463" s="8" t="n"/>
       <c r="I463" s="8" t="n"/>
@@ -16828,8 +16825,8 @@
         <f>IF(C464="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E464" s="16" t="n"/>
-      <c r="F464" s="16" t="n"/>
+      <c r="E464" s="9" t="n"/>
+      <c r="F464" s="9" t="n"/>
       <c r="G464" s="8" t="n"/>
       <c r="H464" s="8" t="n"/>
       <c r="I464" s="8" t="n"/>
@@ -16862,8 +16859,8 @@
         <f>IF(C465="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E465" s="16" t="n"/>
-      <c r="F465" s="16" t="n"/>
+      <c r="E465" s="9" t="n"/>
+      <c r="F465" s="9" t="n"/>
       <c r="G465" s="8" t="n"/>
       <c r="H465" s="8" t="n"/>
       <c r="I465" s="8" t="n"/>
@@ -16896,8 +16893,8 @@
         <f>IF(C466="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E466" s="16" t="n"/>
-      <c r="F466" s="16" t="n"/>
+      <c r="E466" s="9" t="n"/>
+      <c r="F466" s="9" t="n"/>
       <c r="G466" s="8" t="n"/>
       <c r="H466" s="8" t="n"/>
       <c r="I466" s="8" t="n"/>
@@ -16930,8 +16927,8 @@
         <f>IF(C467="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E467" s="16" t="n"/>
-      <c r="F467" s="16" t="n"/>
+      <c r="E467" s="9" t="n"/>
+      <c r="F467" s="9" t="n"/>
       <c r="G467" s="8" t="n"/>
       <c r="H467" s="8" t="n"/>
       <c r="I467" s="8" t="n"/>
@@ -16964,8 +16961,8 @@
         <f>IF(C468="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E468" s="16" t="n"/>
-      <c r="F468" s="16" t="n"/>
+      <c r="E468" s="9" t="n"/>
+      <c r="F468" s="9" t="n"/>
       <c r="G468" s="8" t="n"/>
       <c r="H468" s="8" t="n"/>
       <c r="I468" s="8" t="n"/>
@@ -16998,8 +16995,8 @@
         <f>IF(C469="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E469" s="16" t="n"/>
-      <c r="F469" s="16" t="n"/>
+      <c r="E469" s="9" t="n"/>
+      <c r="F469" s="9" t="n"/>
       <c r="G469" s="8" t="n"/>
       <c r="H469" s="8" t="n"/>
       <c r="I469" s="8" t="n"/>
@@ -17032,8 +17029,8 @@
         <f>IF(C470="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E470" s="16" t="n"/>
-      <c r="F470" s="16" t="n"/>
+      <c r="E470" s="9" t="n"/>
+      <c r="F470" s="9" t="n"/>
       <c r="G470" s="8" t="n"/>
       <c r="H470" s="8" t="n"/>
       <c r="I470" s="8" t="n"/>
@@ -17066,8 +17063,8 @@
         <f>IF(C471="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E471" s="16" t="n"/>
-      <c r="F471" s="16" t="n"/>
+      <c r="E471" s="9" t="n"/>
+      <c r="F471" s="9" t="n"/>
       <c r="G471" s="8" t="n"/>
       <c r="H471" s="8" t="n"/>
       <c r="I471" s="8" t="n"/>
@@ -17100,8 +17097,8 @@
         <f>IF(C472="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E472" s="16" t="n"/>
-      <c r="F472" s="16" t="n"/>
+      <c r="E472" s="9" t="n"/>
+      <c r="F472" s="9" t="n"/>
       <c r="G472" s="8" t="n"/>
       <c r="H472" s="8" t="n"/>
       <c r="I472" s="8" t="n"/>
@@ -17134,8 +17131,8 @@
         <f>IF(C473="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E473" s="16" t="n"/>
-      <c r="F473" s="16" t="n"/>
+      <c r="E473" s="9" t="n"/>
+      <c r="F473" s="9" t="n"/>
       <c r="G473" s="8" t="n"/>
       <c r="H473" s="8" t="n"/>
       <c r="I473" s="8" t="n"/>
@@ -17168,8 +17165,8 @@
         <f>IF(C474="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E474" s="16" t="n"/>
-      <c r="F474" s="16" t="n"/>
+      <c r="E474" s="9" t="n"/>
+      <c r="F474" s="9" t="n"/>
       <c r="G474" s="8" t="n"/>
       <c r="H474" s="8" t="n"/>
       <c r="I474" s="8" t="n"/>
@@ -17202,8 +17199,8 @@
         <f>IF(C475="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E475" s="16" t="n"/>
-      <c r="F475" s="16" t="n"/>
+      <c r="E475" s="9" t="n"/>
+      <c r="F475" s="9" t="n"/>
       <c r="G475" s="8" t="n"/>
       <c r="H475" s="8" t="n"/>
       <c r="I475" s="8" t="n"/>
@@ -17236,8 +17233,8 @@
         <f>IF(C476="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E476" s="16" t="n"/>
-      <c r="F476" s="16" t="n"/>
+      <c r="E476" s="9" t="n"/>
+      <c r="F476" s="9" t="n"/>
       <c r="G476" s="8" t="n"/>
       <c r="H476" s="8" t="n"/>
       <c r="I476" s="8" t="n"/>
@@ -17270,8 +17267,8 @@
         <f>IF(C477="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E477" s="16" t="n"/>
-      <c r="F477" s="16" t="n"/>
+      <c r="E477" s="9" t="n"/>
+      <c r="F477" s="9" t="n"/>
       <c r="G477" s="8" t="n"/>
       <c r="H477" s="8" t="n"/>
       <c r="I477" s="8" t="n"/>
@@ -17304,8 +17301,8 @@
         <f>IF(C478="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E478" s="16" t="n"/>
-      <c r="F478" s="16" t="n"/>
+      <c r="E478" s="9" t="n"/>
+      <c r="F478" s="9" t="n"/>
       <c r="G478" s="8" t="n"/>
       <c r="H478" s="8" t="n"/>
       <c r="I478" s="8" t="n"/>
@@ -17338,8 +17335,8 @@
         <f>IF(C479="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E479" s="16" t="n"/>
-      <c r="F479" s="16" t="n"/>
+      <c r="E479" s="9" t="n"/>
+      <c r="F479" s="9" t="n"/>
       <c r="G479" s="8" t="n"/>
       <c r="H479" s="8" t="n"/>
       <c r="I479" s="8" t="n"/>
@@ -17372,8 +17369,8 @@
         <f>IF(C480="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E480" s="16" t="n"/>
-      <c r="F480" s="16" t="n"/>
+      <c r="E480" s="9" t="n"/>
+      <c r="F480" s="9" t="n"/>
       <c r="G480" s="8" t="n"/>
       <c r="H480" s="8" t="n"/>
       <c r="I480" s="8" t="n"/>
@@ -17406,8 +17403,8 @@
         <f>IF(C481="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E481" s="16" t="n"/>
-      <c r="F481" s="16" t="n"/>
+      <c r="E481" s="9" t="n"/>
+      <c r="F481" s="9" t="n"/>
       <c r="G481" s="8" t="n"/>
       <c r="H481" s="8" t="n"/>
       <c r="I481" s="8" t="n"/>
@@ -17440,8 +17437,8 @@
         <f>IF(C482="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E482" s="16" t="n"/>
-      <c r="F482" s="16" t="n"/>
+      <c r="E482" s="9" t="n"/>
+      <c r="F482" s="9" t="n"/>
       <c r="G482" s="8" t="n"/>
       <c r="H482" s="8" t="n"/>
       <c r="I482" s="8" t="n"/>
@@ -17474,8 +17471,8 @@
         <f>IF(C483="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E483" s="16" t="n"/>
-      <c r="F483" s="16" t="n"/>
+      <c r="E483" s="9" t="n"/>
+      <c r="F483" s="9" t="n"/>
       <c r="G483" s="8" t="n"/>
       <c r="H483" s="8" t="n"/>
       <c r="I483" s="8" t="n"/>
@@ -17508,8 +17505,8 @@
         <f>IF(C484="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E484" s="16" t="n"/>
-      <c r="F484" s="16" t="n"/>
+      <c r="E484" s="9" t="n"/>
+      <c r="F484" s="9" t="n"/>
       <c r="G484" s="8" t="n"/>
       <c r="H484" s="8" t="n"/>
       <c r="I484" s="8" t="n"/>
@@ -17542,8 +17539,8 @@
         <f>IF(C485="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E485" s="16" t="n"/>
-      <c r="F485" s="16" t="n"/>
+      <c r="E485" s="9" t="n"/>
+      <c r="F485" s="9" t="n"/>
       <c r="G485" s="8" t="n"/>
       <c r="H485" s="8" t="n"/>
       <c r="I485" s="8" t="n"/>
@@ -17576,8 +17573,8 @@
         <f>IF(C486="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E486" s="16" t="n"/>
-      <c r="F486" s="16" t="n"/>
+      <c r="E486" s="9" t="n"/>
+      <c r="F486" s="9" t="n"/>
       <c r="G486" s="8" t="n"/>
       <c r="H486" s="8" t="n"/>
       <c r="I486" s="8" t="n"/>
@@ -17610,8 +17607,8 @@
         <f>IF(C487="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E487" s="16" t="n"/>
-      <c r="F487" s="16" t="n"/>
+      <c r="E487" s="9" t="n"/>
+      <c r="F487" s="9" t="n"/>
       <c r="G487" s="8" t="n"/>
       <c r="H487" s="8" t="n"/>
       <c r="I487" s="8" t="n"/>
@@ -17644,8 +17641,8 @@
         <f>IF(C488="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E488" s="16" t="n"/>
-      <c r="F488" s="16" t="n"/>
+      <c r="E488" s="9" t="n"/>
+      <c r="F488" s="9" t="n"/>
       <c r="G488" s="8" t="n"/>
       <c r="H488" s="8" t="n"/>
       <c r="I488" s="8" t="n"/>
@@ -17678,8 +17675,8 @@
         <f>IF(C489="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E489" s="16" t="n"/>
-      <c r="F489" s="16" t="n"/>
+      <c r="E489" s="9" t="n"/>
+      <c r="F489" s="9" t="n"/>
       <c r="G489" s="8" t="n"/>
       <c r="H489" s="8" t="n"/>
       <c r="I489" s="8" t="n"/>
@@ -17712,8 +17709,8 @@
         <f>IF(C490="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E490" s="16" t="n"/>
-      <c r="F490" s="16" t="n"/>
+      <c r="E490" s="9" t="n"/>
+      <c r="F490" s="9" t="n"/>
       <c r="G490" s="8" t="n"/>
       <c r="H490" s="8" t="n"/>
       <c r="I490" s="8" t="n"/>
@@ -17746,8 +17743,8 @@
         <f>IF(C491="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E491" s="16" t="n"/>
-      <c r="F491" s="16" t="n"/>
+      <c r="E491" s="9" t="n"/>
+      <c r="F491" s="9" t="n"/>
       <c r="G491" s="8" t="n"/>
       <c r="H491" s="8" t="n"/>
       <c r="I491" s="8" t="n"/>
@@ -17780,8 +17777,8 @@
         <f>IF(C492="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E492" s="16" t="n"/>
-      <c r="F492" s="16" t="n"/>
+      <c r="E492" s="9" t="n"/>
+      <c r="F492" s="9" t="n"/>
       <c r="G492" s="8" t="n"/>
       <c r="H492" s="8" t="n"/>
       <c r="I492" s="8" t="n"/>
@@ -17814,8 +17811,8 @@
         <f>IF(C493="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E493" s="16" t="n"/>
-      <c r="F493" s="16" t="n"/>
+      <c r="E493" s="9" t="n"/>
+      <c r="F493" s="9" t="n"/>
       <c r="G493" s="8" t="n"/>
       <c r="H493" s="8" t="n"/>
       <c r="I493" s="8" t="n"/>
@@ -17848,8 +17845,8 @@
         <f>IF(C494="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E494" s="16" t="n"/>
-      <c r="F494" s="16" t="n"/>
+      <c r="E494" s="9" t="n"/>
+      <c r="F494" s="9" t="n"/>
       <c r="G494" s="8" t="n"/>
       <c r="H494" s="8" t="n"/>
       <c r="I494" s="8" t="n"/>
@@ -17882,8 +17879,8 @@
         <f>IF(C495="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E495" s="16" t="n"/>
-      <c r="F495" s="16" t="n"/>
+      <c r="E495" s="9" t="n"/>
+      <c r="F495" s="9" t="n"/>
       <c r="G495" s="8" t="n"/>
       <c r="H495" s="8" t="n"/>
       <c r="I495" s="8" t="n"/>
@@ -17916,8 +17913,8 @@
         <f>IF(C496="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E496" s="16" t="n"/>
-      <c r="F496" s="16" t="n"/>
+      <c r="E496" s="9" t="n"/>
+      <c r="F496" s="9" t="n"/>
       <c r="G496" s="8" t="n"/>
       <c r="H496" s="8" t="n"/>
       <c r="I496" s="8" t="n"/>
@@ -17950,8 +17947,8 @@
         <f>IF(C497="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E497" s="16" t="n"/>
-      <c r="F497" s="16" t="n"/>
+      <c r="E497" s="9" t="n"/>
+      <c r="F497" s="9" t="n"/>
       <c r="G497" s="8" t="n"/>
       <c r="H497" s="8" t="n"/>
       <c r="I497" s="8" t="n"/>
@@ -17984,8 +17981,8 @@
         <f>IF(C498="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E498" s="16" t="n"/>
-      <c r="F498" s="16" t="n"/>
+      <c r="E498" s="9" t="n"/>
+      <c r="F498" s="9" t="n"/>
       <c r="G498" s="8" t="n"/>
       <c r="H498" s="8" t="n"/>
       <c r="I498" s="8" t="n"/>
@@ -18018,8 +18015,8 @@
         <f>IF(C499="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E499" s="16" t="n"/>
-      <c r="F499" s="16" t="n"/>
+      <c r="E499" s="9" t="n"/>
+      <c r="F499" s="9" t="n"/>
       <c r="G499" s="8" t="n"/>
       <c r="H499" s="8" t="n"/>
       <c r="I499" s="8" t="n"/>
@@ -18052,8 +18049,8 @@
         <f>IF(C500="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E500" s="16" t="n"/>
-      <c r="F500" s="16" t="n"/>
+      <c r="E500" s="9" t="n"/>
+      <c r="F500" s="9" t="n"/>
       <c r="G500" s="8" t="n"/>
       <c r="H500" s="8" t="n"/>
       <c r="I500" s="8" t="n"/>
@@ -18086,8 +18083,8 @@
         <f>IF(C501="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
       </c>
-      <c r="E501" s="16" t="n"/>
-      <c r="F501" s="16" t="n"/>
+      <c r="E501" s="9" t="n"/>
+      <c r="F501" s="9" t="n"/>
       <c r="G501" s="8" t="n"/>
       <c r="H501" s="8" t="n"/>
       <c r="I501" s="8" t="n"/>

--- a/pdtracker/cursive_Trial_Template.xlsx
+++ b/pdtracker/cursive_Trial_Template.xlsx
@@ -937,20 +937,12 @@
       <c r="Z1" s="8" t="n"/>
     </row>
     <row r="2" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A2" s="9" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="A2" s="9" t="n"/>
       <c r="B2" s="10">
         <f>IF(A2="","",IF(A2="Amazon","ASIN",IF(A2="Flipkart","FSN",IF(A2="Meesho","Product ID",IF(A2="Myntra","Style ID",IF(A2="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>B0B561VFWK</t>
-        </is>
-      </c>
+      <c r="C2" s="12" t="n"/>
       <c r="D2" s="11">
         <f>IF(C2="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -979,20 +971,12 @@
       <c r="Z2" s="8" t="n"/>
     </row>
     <row r="3" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A3" s="9" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="A3" s="9" t="n"/>
       <c r="B3" s="10">
         <f>IF(A3="","",IF(A3="Amazon","ASIN",IF(A3="Flipkart","FSN",IF(A3="Meesho","Product ID",IF(A3="Myntra","Style ID",IF(A3="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>B0F1MWJV6Z</t>
-        </is>
-      </c>
+      <c r="C3" s="12" t="n"/>
       <c r="D3" s="11">
         <f>IF(C3="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1021,20 +1005,12 @@
       <c r="Z3" s="8" t="n"/>
     </row>
     <row r="4" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A4" s="9" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="A4" s="9" t="n"/>
       <c r="B4" s="10">
         <f>IF(A4="","",IF(A4="Amazon","ASIN",IF(A4="Flipkart","FSN",IF(A4="Meesho","Product ID",IF(A4="Myntra","Style ID",IF(A4="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>B0D7VW9ZC9</t>
-        </is>
-      </c>
+      <c r="C4" s="12" t="n"/>
       <c r="D4" s="11">
         <f>IF(C4="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1063,20 +1039,12 @@
       <c r="Z4" s="8" t="n"/>
     </row>
     <row r="5" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="10">
         <f>IF(A5="","",IF(A5="Amazon","ASIN",IF(A5="Flipkart","FSN",IF(A5="Meesho","Product ID",IF(A5="Myntra","Style ID",IF(A5="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>B0BCKMZY1V</t>
-        </is>
-      </c>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="11">
         <f>IF(C5="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1105,20 +1073,12 @@
       <c r="Z5" s="8" t="n"/>
     </row>
     <row r="6" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
+      <c r="A6" s="9" t="n"/>
       <c r="B6" s="10">
         <f>IF(A6="","",IF(A6="Amazon","ASIN",IF(A6="Flipkart","FSN",IF(A6="Meesho","Product ID",IF(A6="Myntra","Style ID",IF(A6="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>B0G6DVB6DG</t>
-        </is>
-      </c>
+      <c r="C6" s="12" t="n"/>
       <c r="D6" s="11">
         <f>IF(C6="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1147,20 +1107,12 @@
       <c r="Z6" s="8" t="n"/>
     </row>
     <row r="7" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Flipkart</t>
-        </is>
-      </c>
+      <c r="A7" s="9" t="n"/>
       <c r="B7" s="10">
         <f>IF(A7="","",IF(A7="Amazon","ASIN",IF(A7="Flipkart","FSN",IF(A7="Meesho","Product ID",IF(A7="Myntra","Style ID",IF(A7="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>SMWGEH7WC8F4VKKZ</t>
-        </is>
-      </c>
+      <c r="C7" s="12" t="n"/>
       <c r="D7" s="11">
         <f>IF(C7="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1189,20 +1141,12 @@
       <c r="Z7" s="8" t="n"/>
     </row>
     <row r="8" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Flipkart</t>
-        </is>
-      </c>
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="10">
         <f>IF(A8="","",IF(A8="Amazon","ASIN",IF(A8="Flipkart","FSN",IF(A8="Meesho","Product ID",IF(A8="Myntra","Style ID",IF(A8="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>SMWH44GEGTYQHPJ2</t>
-        </is>
-      </c>
+      <c r="C8" s="12" t="n"/>
       <c r="D8" s="11">
         <f>IF(C8="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1231,20 +1175,12 @@
       <c r="Z8" s="8" t="n"/>
     </row>
     <row r="9" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Flipkart</t>
-        </is>
-      </c>
+      <c r="A9" s="9" t="n"/>
       <c r="B9" s="10">
         <f>IF(A9="","",IF(A9="Amazon","ASIN",IF(A9="Flipkart","FSN",IF(A9="Meesho","Product ID",IF(A9="Myntra","Style ID",IF(A9="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>DUBHDFF7D3JV7ZFY</t>
-        </is>
-      </c>
+      <c r="C9" s="12" t="n"/>
       <c r="D9" s="11">
         <f>IF(C9="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1273,20 +1209,12 @@
       <c r="Z9" s="8" t="n"/>
     </row>
     <row r="10" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Flipkart</t>
-        </is>
-      </c>
+      <c r="A10" s="9" t="n"/>
       <c r="B10" s="10">
         <f>IF(A10="","",IF(A10="Amazon","ASIN",IF(A10="Flipkart","FSN",IF(A10="Meesho","Product ID",IF(A10="Myntra","Style ID",IF(A10="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>SMWGQHN4RWUTXYMY</t>
-        </is>
-      </c>
+      <c r="C10" s="12" t="n"/>
       <c r="D10" s="11">
         <f>IF(C10="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1315,20 +1243,12 @@
       <c r="Z10" s="8" t="n"/>
     </row>
     <row r="11" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Flipkart</t>
-        </is>
-      </c>
+      <c r="A11" s="9" t="n"/>
       <c r="B11" s="10">
         <f>IF(A11="","",IF(A11="Amazon","ASIN",IF(A11="Flipkart","FSN",IF(A11="Meesho","Product ID",IF(A11="Myntra","Style ID",IF(A11="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>FLTHC44PVYHFYDQG</t>
-        </is>
-      </c>
+      <c r="C11" s="12" t="n"/>
       <c r="D11" s="11">
         <f>IF(C11="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1357,18 +1277,12 @@
       <c r="Z11" s="8" t="n"/>
     </row>
     <row r="12" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Myntra</t>
-        </is>
-      </c>
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="10">
         <f>IF(A12="","",IF(A12="Amazon","ASIN",IF(A12="Flipkart","FSN",IF(A12="Meesho","Product ID",IF(A12="Myntra","Style ID",IF(A12="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C12" s="13" t="n">
-        <v>31666100</v>
-      </c>
+      <c r="C12" s="13" t="n"/>
       <c r="D12" s="11">
         <f>IF(C12="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1397,18 +1311,12 @@
       <c r="Z12" s="8" t="n"/>
     </row>
     <row r="13" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Myntra</t>
-        </is>
-      </c>
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="10">
         <f>IF(A13="","",IF(A13="Amazon","ASIN",IF(A13="Flipkart","FSN",IF(A13="Meesho","Product ID",IF(A13="Myntra","Style ID",IF(A13="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C13" s="13" t="n">
-        <v>25542452</v>
-      </c>
+      <c r="C13" s="13" t="n"/>
       <c r="D13" s="11">
         <f>IF(C13="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1437,18 +1345,12 @@
       <c r="Z13" s="8" t="n"/>
     </row>
     <row r="14" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Myntra</t>
-        </is>
-      </c>
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="10">
         <f>IF(A14="","",IF(A14="Amazon","ASIN",IF(A14="Flipkart","FSN",IF(A14="Meesho","Product ID",IF(A14="Myntra","Style ID",IF(A14="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C14" s="13" t="n">
-        <v>17668462</v>
-      </c>
+      <c r="C14" s="13" t="n"/>
       <c r="D14" s="11">
         <f>IF(C14="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1477,18 +1379,12 @@
       <c r="Z14" s="8" t="n"/>
     </row>
     <row r="15" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Myntra</t>
-        </is>
-      </c>
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="10">
         <f>IF(A15="","",IF(A15="Amazon","ASIN",IF(A15="Flipkart","FSN",IF(A15="Meesho","Product ID",IF(A15="Myntra","Style ID",IF(A15="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C15" s="13" t="n">
-        <v>14035144</v>
-      </c>
+      <c r="C15" s="13" t="n"/>
       <c r="D15" s="11">
         <f>IF(C15="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1517,18 +1413,12 @@
       <c r="Z15" s="8" t="n"/>
     </row>
     <row r="16" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Myntra</t>
-        </is>
-      </c>
+      <c r="A16" s="9" t="n"/>
       <c r="B16" s="10">
         <f>IF(A16="","",IF(A16="Amazon","ASIN",IF(A16="Flipkart","FSN",IF(A16="Meesho","Product ID",IF(A16="Myntra","Style ID",IF(A16="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C16" s="13" t="n">
-        <v>9162839</v>
-      </c>
+      <c r="C16" s="13" t="n"/>
       <c r="D16" s="11">
         <f>IF(C16="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1557,18 +1447,12 @@
       <c r="Z16" s="8" t="n"/>
     </row>
     <row r="17" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
+      <c r="A17" s="9" t="n"/>
       <c r="B17" s="10">
         <f>IF(A17="","",IF(A17="Amazon","ASIN",IF(A17="Flipkart","FSN",IF(A17="Meesho","Product ID",IF(A17="Myntra","Style ID",IF(A17="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C17" s="13" t="n">
-        <v>3391720</v>
-      </c>
+      <c r="C17" s="13" t="n"/>
       <c r="D17" s="11">
         <f>IF(C17="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1597,18 +1481,12 @@
       <c r="Z17" s="8" t="n"/>
     </row>
     <row r="18" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
+      <c r="A18" s="9" t="n"/>
       <c r="B18" s="10">
         <f>IF(A18="","",IF(A18="Amazon","ASIN",IF(A18="Flipkart","FSN",IF(A18="Meesho","Product ID",IF(A18="Myntra","Style ID",IF(A18="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C18" s="13" t="n">
-        <v>16190242</v>
-      </c>
+      <c r="C18" s="13" t="n"/>
       <c r="D18" s="11">
         <f>IF(C18="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1637,18 +1515,12 @@
       <c r="Z18" s="8" t="n"/>
     </row>
     <row r="19" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
+      <c r="A19" s="9" t="n"/>
       <c r="B19" s="10">
         <f>IF(A19="","",IF(A19="Amazon","ASIN",IF(A19="Flipkart","FSN",IF(A19="Meesho","Product ID",IF(A19="Myntra","Style ID",IF(A19="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C19" s="13" t="n">
-        <v>21103392</v>
-      </c>
+      <c r="C19" s="13" t="n"/>
       <c r="D19" s="11">
         <f>IF(C19="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1677,18 +1549,12 @@
       <c r="Z19" s="8" t="n"/>
     </row>
     <row r="20" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="10">
         <f>IF(A20="","",IF(A20="Amazon","ASIN",IF(A20="Flipkart","FSN",IF(A20="Meesho","Product ID",IF(A20="Myntra","Style ID",IF(A20="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C20" s="13" t="n">
-        <v>8225317</v>
-      </c>
+      <c r="C20" s="13" t="n"/>
       <c r="D20" s="11">
         <f>IF(C20="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1717,18 +1583,12 @@
       <c r="Z20" s="8" t="n"/>
     </row>
     <row r="21" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>FirstCry</t>
-        </is>
-      </c>
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="10">
         <f>IF(A21="","",IF(A21="Amazon","ASIN",IF(A21="Flipkart","FSN",IF(A21="Meesho","Product ID",IF(A21="Myntra","Style ID",IF(A21="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C21" s="13" t="n">
-        <v>20471677</v>
-      </c>
+      <c r="C21" s="13" t="n"/>
       <c r="D21" s="11">
         <f>IF(C21="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1757,18 +1617,12 @@
       <c r="Z21" s="8" t="n"/>
     </row>
     <row r="22" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Meesho</t>
-        </is>
-      </c>
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="10">
         <f>IF(A22="","",IF(A22="Amazon","ASIN",IF(A22="Flipkart","FSN",IF(A22="Meesho","Product ID",IF(A22="Myntra","Style ID",IF(A22="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C22" s="13" t="n">
-        <v>44175508</v>
-      </c>
+      <c r="C22" s="13" t="n"/>
       <c r="D22" s="11">
         <f>IF(C22="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1797,18 +1651,12 @@
       <c r="Z22" s="8" t="n"/>
     </row>
     <row r="23" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Meesho</t>
-        </is>
-      </c>
+      <c r="A23" s="9" t="n"/>
       <c r="B23" s="10">
         <f>IF(A23="","",IF(A23="Amazon","ASIN",IF(A23="Flipkart","FSN",IF(A23="Meesho","Product ID",IF(A23="Myntra","Style ID",IF(A23="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C23" s="13" t="n">
-        <v>490296740</v>
-      </c>
+      <c r="C23" s="13" t="n"/>
       <c r="D23" s="11">
         <f>IF(C23="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1837,18 +1685,12 @@
       <c r="Z23" s="8" t="n"/>
     </row>
     <row r="24" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Meesho</t>
-        </is>
-      </c>
+      <c r="A24" s="9" t="n"/>
       <c r="B24" s="10">
         <f>IF(A24="","",IF(A24="Amazon","ASIN",IF(A24="Flipkart","FSN",IF(A24="Meesho","Product ID",IF(A24="Myntra","Style ID",IF(A24="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C24" s="13" t="n">
-        <v>443545837</v>
-      </c>
+      <c r="C24" s="13" t="n"/>
       <c r="D24" s="11">
         <f>IF(C24="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1877,18 +1719,12 @@
       <c r="Z24" s="8" t="n"/>
     </row>
     <row r="25" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Meesho</t>
-        </is>
-      </c>
+      <c r="A25" s="9" t="n"/>
       <c r="B25" s="10">
         <f>IF(A25="","",IF(A25="Amazon","ASIN",IF(A25="Flipkart","FSN",IF(A25="Meesho","Product ID",IF(A25="Myntra","Style ID",IF(A25="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C25" s="13" t="n">
-        <v>521893927</v>
-      </c>
+      <c r="C25" s="13" t="n"/>
       <c r="D25" s="11">
         <f>IF(C25="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
@@ -1917,18 +1753,12 @@
       <c r="Z25" s="8" t="n"/>
     </row>
     <row r="26" ht="21.95" customHeight="1" thickBot="1">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Meesho</t>
-        </is>
-      </c>
+      <c r="A26" s="9" t="n"/>
       <c r="B26" s="10">
         <f>IF(A26="","",IF(A26="Amazon","ASIN",IF(A26="Flipkart","FSN",IF(A26="Meesho","Product ID",IF(A26="Myntra","Style ID",IF(A26="FirstCry","FC ID",""))))))</f>
         <v/>
       </c>
-      <c r="C26" s="13" t="n">
-        <v>163095016</v>
-      </c>
+      <c r="C26" s="13" t="n"/>
       <c r="D26" s="11">
         <f>IF(C26="","","⚠ Once uploaded, this row cannot be edited. Please double-check Platform and Product ID before uploading.")</f>
         <v/>
